--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -36,13 +36,49 @@
     <t>Help</t>
   </si>
   <si>
-    <t>""</t>
+    <t>虹の精霊石</t>
+  </si>
+  <si>
+    <t>Rank.Nの魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>炎の精霊石</t>
+  </si>
+  <si>
+    <t>Rank.Nの炎属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>雷の精霊石</t>
+  </si>
+  <si>
+    <t>Rank.Nの雷属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>氷の精霊石</t>
+  </si>
+  <si>
+    <t>Rank.Nの氷属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>光の精霊石</t>
+  </si>
+  <si>
+    <t>Rank.Nの光属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>闇の精霊石</t>
+  </si>
+  <si>
+    <t>Rank.Nの闇属性魔法をランダムで入手</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
     <t>LearnSkill</t>
+  </si>
+  <si>
+    <t>Param1=Rank,Param2=属性</t>
   </si>
 </sst>
 </file>
@@ -51,9 +87,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -73,58 +109,51 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -140,6 +169,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -162,6 +198,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -179,23 +223,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,19 +260,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -254,7 +398,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -266,67 +416,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -338,73 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,24 +456,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -481,11 +504,35 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -504,17 +551,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -523,145 +559,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -991,7 +1027,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1010,17 +1046,90 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
+        <v>1000</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>1010</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>1020</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>1030</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>1040</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>1050</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="6:6">
+      <c r="F14" s="1"/>
     </row>
     <row r="15" spans="6:6">
       <c r="F15" s="1"/>
@@ -1039,9 +1148,6 @@
     </row>
     <row r="20" spans="6:6">
       <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="6:6">
-      <c r="F21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1052,8 +1158,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -1068,13 +1177,68 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1010</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1020</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1030</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>1040</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>1050</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1086,20 +1250,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <t>Type</t>
   </si>
   <si>
-    <t>LearnSkill</t>
+    <t>RandumAddSkill</t>
   </si>
   <si>
     <t>Param1=Rank,Param2=属性</t>
@@ -86,9 +86,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -107,68 +107,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,15 +236,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,187 +260,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,17 +451,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -551,6 +540,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -559,16 +559,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -577,28 +577,28 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -607,97 +607,97 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -72,6 +72,12 @@
     <t>Rank.Nの闇属性魔法をランダムで入手</t>
   </si>
   <si>
+    <t>ヒールユニット</t>
+  </si>
+  <si>
+    <t>評価値+10</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -79,6 +85,12 @@
   </si>
   <si>
     <t>Param1=Rank,Param2=属性</t>
+  </si>
+  <si>
+    <t>Artifact</t>
+  </si>
+  <si>
+    <t>Param1=スキルId</t>
   </si>
 </sst>
 </file>
@@ -86,10 +98,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -108,73 +120,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -188,6 +134,66 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -196,9 +202,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,39 +256,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,97 +272,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,85 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,17 +466,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -484,44 +492,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -543,11 +524,42 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -559,145 +571,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1128,6 +1140,20 @@
         <v>5</v>
       </c>
     </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2010</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>310010</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
     <row r="14" spans="6:6">
       <c r="F14" s="1"/>
     </row>
@@ -1158,9 +1184,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
+    <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
     <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1239,6 +1266,17 @@
       </c>
       <c r="C7" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>2010</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1250,12 +1288,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="15.5454545454545" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1263,10 +1304,21 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>評価値+10</t>
+  </si>
+  <si>
+    <t>月のかけら</t>
   </si>
   <si>
     <t>Type</t>
@@ -98,10 +101,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -116,6 +119,67 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -134,130 +198,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,13 +275,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -290,163 +425,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -468,10 +471,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -488,6 +489,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,15 +541,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -544,22 +551,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -571,16 +574,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -589,127 +592,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1154,6 +1157,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2020</v>
+      </c>
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>310020</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
     <row r="14" spans="6:6">
       <c r="F14" s="1"/>
     </row>
@@ -1184,8 +1201,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
     <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
@@ -1276,6 +1293,17 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>2020</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1296,7 +1324,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1304,10 +1332,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1315,10 +1343,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -103,8 +103,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -119,6 +119,22 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -130,36 +146,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -168,28 +154,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -198,8 +162,75 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -207,19 +238,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -227,40 +259,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -275,43 +275,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -323,139 +455,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,11 +469,56 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -493,47 +538,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -555,17 +566,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -574,16 +574,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -592,127 +592,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>Id</t>
   </si>
@@ -72,13 +72,19 @@
     <t>Rank.Nの闇属性魔法をランダムで入手</t>
   </si>
   <si>
+    <t>妖精の祈り</t>
+  </si>
+  <si>
+    <t>評価値+10</t>
+  </si>
+  <si>
+    <t>月のかけら</t>
+  </si>
+  <si>
+    <t>錬金術師の遺稿</t>
+  </si>
+  <si>
     <t>ヒールユニット</t>
-  </si>
-  <si>
-    <t>評価値+10</t>
-  </si>
-  <si>
-    <t>月のかけら</t>
   </si>
   <si>
     <t>Type</t>
@@ -101,8 +107,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -122,8 +128,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -133,6 +175,45 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -146,11 +227,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -163,104 +259,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -275,187 +281,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -466,6 +472,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -480,30 +510,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -523,17 +529,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -549,20 +558,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -574,7 +580,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -583,7 +589,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -592,127 +598,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1042,7 +1048,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1171,8 +1177,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="6:6">
-      <c r="F14" s="1"/>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2030</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <v>310030</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2130</v>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>310130</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="6:6">
       <c r="F15" s="1"/>
@@ -1191,6 +1222,9 @@
     </row>
     <row r="20" spans="6:6">
       <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="6:6">
+      <c r="F21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1201,7 +1235,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -1304,6 +1338,28 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>2030</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>2130</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1324,7 +1380,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1332,10 +1388,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1343,10 +1399,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -75,7 +75,7 @@
     <t>妖精の祈り</t>
   </si>
   <si>
-    <t>評価値+10</t>
+    <t>評価値+5</t>
   </si>
   <si>
     <t>月のかけら</t>
@@ -107,10 +107,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -129,13 +129,87 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -143,63 +217,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -213,6 +235,29 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -220,53 +265,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,187 +281,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -472,6 +472,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -493,23 +532,28 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -528,50 +572,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -580,145 +580,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>Id</t>
   </si>
@@ -70,6 +70,42 @@
   </si>
   <si>
     <t>Rank.Nの闇属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>虹の魔晶石</t>
+  </si>
+  <si>
+    <t>Rank.Rの魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>炎の魔晶石</t>
+  </si>
+  <si>
+    <t>Rank.Rの炎属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>雷の魔晶石</t>
+  </si>
+  <si>
+    <t>Rank.Rの雷属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>氷の魔晶石</t>
+  </si>
+  <si>
+    <t>Rank.Rの氷属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>光の魔晶石</t>
+  </si>
+  <si>
+    <t>Rank.Rの光属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>闇の魔晶石</t>
+  </si>
+  <si>
+    <t>Rank.Rの闇属性魔法をランダムで入手</t>
   </si>
   <si>
     <t>妖精の祈り</t>
@@ -108,9 +144,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -129,12 +165,58 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -143,25 +225,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -173,35 +261,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -235,38 +295,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,43 +317,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,139 +491,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -472,6 +508,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -507,9 +552,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -538,26 +594,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -580,145 +616,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1048,7 +1084,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1151,80 +1187,164 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>2010</v>
+        <v>1100</v>
       </c>
       <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
         <v>20</v>
       </c>
-      <c r="C8">
-        <v>310010</v>
-      </c>
       <c r="D8">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>2020</v>
+        <v>1110</v>
       </c>
       <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9">
         <v>20</v>
       </c>
-      <c r="C9">
-        <v>310020</v>
-      </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>2030</v>
+        <v>1120</v>
       </c>
       <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
         <v>20</v>
       </c>
-      <c r="C10">
-        <v>310030</v>
-      </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
+        <v>1130</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>1140</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>1150</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2010</v>
+      </c>
+      <c r="B14">
+        <v>20</v>
+      </c>
+      <c r="C14">
+        <v>310010</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>2020</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>310020</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>2030</v>
+      </c>
+      <c r="B16">
+        <v>20</v>
+      </c>
+      <c r="C16">
+        <v>310030</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
         <v>2130</v>
       </c>
-      <c r="B11">
+      <c r="B17">
         <v>20</v>
       </c>
-      <c r="C11">
+      <c r="C17">
         <v>310130</v>
       </c>
-      <c r="D11">
+      <c r="D17">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="6:6">
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="6:6">
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="6:6">
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="6:6">
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="6:6">
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="6:6">
-      <c r="F20" s="1"/>
     </row>
     <row r="21" spans="6:6">
       <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="6:6">
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="6:6">
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="6:6">
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="6:6">
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="6:6">
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="6:6">
+      <c r="F27" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1235,7 +1355,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -1321,7 +1441,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>2010</v>
+        <v>1100</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
@@ -1332,35 +1452,101 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2020</v>
+        <v>1110</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2030</v>
+        <v>1120</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
+        <v>1130</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>1140</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>1150</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>2010</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>2020</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>2030</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>2130</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1566,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1388,10 +1574,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1399,10 +1585,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>錬金術師の遺稿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ワタリガラスの旗 </t>
   </si>
   <si>
     <t>ヒールユニット</t>
@@ -144,8 +147,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -165,6 +168,90 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -172,81 +259,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -261,46 +304,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -317,55 +320,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,127 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -514,8 +517,34 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -550,36 +579,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -594,17 +603,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,145 +619,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1313,15 +1316,29 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>2130</v>
+        <v>2040</v>
       </c>
       <c r="B17">
         <v>20</v>
       </c>
       <c r="C17">
+        <v>310040</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>2130</v>
+      </c>
+      <c r="B18">
+        <v>20</v>
+      </c>
+      <c r="C18">
         <v>310130</v>
       </c>
-      <c r="D17">
+      <c r="D18">
         <v>0</v>
       </c>
     </row>
@@ -1355,7 +1372,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -1540,12 +1557,23 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>2130</v>
+        <v>2040</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>2130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1566,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1574,10 +1602,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1585,10 +1613,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
   <si>
     <t>Id</t>
   </si>
@@ -36,76 +36,112 @@
     <t>Help</t>
   </si>
   <si>
-    <t>虹の精霊石</t>
-  </si>
-  <si>
-    <t>Rank.Nの魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>炎の精霊石</t>
-  </si>
-  <si>
-    <t>Rank.Nの炎属性魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>雷の精霊石</t>
-  </si>
-  <si>
-    <t>Rank.Nの雷属性魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>氷の精霊石</t>
-  </si>
-  <si>
-    <t>Rank.Nの氷属性魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>光の精霊石</t>
-  </si>
-  <si>
-    <t>Rank.Nの光属性魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>闇の精霊石</t>
-  </si>
-  <si>
-    <t>Rank.Nの闇属性魔法をランダムで入手</t>
+    <t>虹の原石</t>
+  </si>
+  <si>
+    <t>Rank.NのPassive魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>炎の原石</t>
+  </si>
+  <si>
+    <t>Rank.Nの炎属性Passive魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>雷の原石</t>
+  </si>
+  <si>
+    <t>Rank.Nの雷属性Passive魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>氷の原石</t>
+  </si>
+  <si>
+    <t>Rank.Nの氷属性Passive魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>光の原石</t>
+  </si>
+  <si>
+    <t>Rank.Nの光属性Passive魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>闇の原石</t>
+  </si>
+  <si>
+    <t>Rank.Nの闇属性Passive魔法をランダムで入手</t>
   </si>
   <si>
     <t>虹の魔晶石</t>
   </si>
   <si>
-    <t>Rank.Rの魔法をランダムで入手</t>
+    <t>Rank.RのPassive魔法をランダムで入手</t>
   </si>
   <si>
     <t>炎の魔晶石</t>
   </si>
   <si>
-    <t>Rank.Rの炎属性魔法をランダムで入手</t>
+    <t>Rank.Rの炎属性Passive魔法をランダムで入手</t>
   </si>
   <si>
     <t>雷の魔晶石</t>
   </si>
   <si>
-    <t>Rank.Rの雷属性魔法をランダムで入手</t>
+    <t>Rank.Rの雷属性Passive魔法をランダムで入手</t>
   </si>
   <si>
     <t>氷の魔晶石</t>
   </si>
   <si>
-    <t>Rank.Rの氷属性魔法をランダムで入手</t>
+    <t>Rank.Rの氷属性Passive魔法をランダムで入手</t>
   </si>
   <si>
     <t>光の魔晶石</t>
   </si>
   <si>
-    <t>Rank.Rの光属性魔法をランダムで入手</t>
+    <t>Rank.Rの光属性Passive魔法をランダムで入手</t>
   </si>
   <si>
     <t>闇の魔晶石</t>
   </si>
   <si>
-    <t>Rank.Rの闇属性魔法をランダムで入手</t>
+    <t>Rank.Rの闇属性Passive魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>虹の精霊輝石</t>
+  </si>
+  <si>
+    <t>Rank.RのActive魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>炎の精霊輝石</t>
+  </si>
+  <si>
+    <t>Rank.Rの炎属性Active魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>雷の精霊輝石</t>
+  </si>
+  <si>
+    <t>Rank.Rの雷属性Active魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>氷の精霊輝石</t>
+  </si>
+  <si>
+    <t>Rank.Rの氷属性Active魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>光の精霊輝石</t>
+  </si>
+  <si>
+    <t>Rank.Rの光属性Active魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>闇の精霊輝石</t>
+  </si>
+  <si>
+    <t>Rank.Rの闇属性Active魔法をランダムで入手</t>
   </si>
   <si>
     <t>妖精の祈り</t>
@@ -121,6 +157,9 @@
   </si>
   <si>
     <t xml:space="preserve">ワタリガラスの旗 </t>
+  </si>
+  <si>
+    <t>先陣の心得</t>
   </si>
   <si>
     <t>ヒールユニット</t>
@@ -168,7 +207,44 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -184,6 +260,61 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -191,7 +322,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -204,112 +349,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -320,19 +359,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,163 +539,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -514,25 +553,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -540,10 +570,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -579,26 +607,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -611,6 +641,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -619,7 +658,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -628,7 +667,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -637,127 +676,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1087,7 +1126,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1274,94 +1313,192 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>2010</v>
+        <v>1200</v>
       </c>
       <c r="B14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>310010</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>2020</v>
+        <v>1210</v>
       </c>
       <c r="B15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>310020</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>2030</v>
+        <v>1220</v>
       </c>
       <c r="B16">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>310030</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>2040</v>
+        <v>1230</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>310040</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
+        <v>1240</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>1250</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>2010</v>
+      </c>
+      <c r="B20">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>310010</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>2020</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>310020</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22">
+        <v>310030</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>2040</v>
+      </c>
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>310040</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>2050</v>
+      </c>
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>310050</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
         <v>2130</v>
       </c>
-      <c r="B18">
+      <c r="B25">
         <v>20</v>
       </c>
-      <c r="C18">
+      <c r="C25">
         <v>310130</v>
       </c>
-      <c r="D18">
+      <c r="D25">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="6:6">
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="6:6">
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="6:6">
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="6:6">
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="6:6">
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="6:6">
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="6:6">
-      <c r="F27" s="1"/>
+    <row r="28" spans="6:6">
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="6:6">
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="6:6">
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="6:6">
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="6:6">
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="6:6">
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="6:6">
+      <c r="F34" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1372,7 +1509,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -1524,7 +1661,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>2010</v>
+        <v>1200</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -1535,46 +1672,123 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>2020</v>
+        <v>1210</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>2030</v>
+        <v>1220</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>2040</v>
+        <v>1230</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
+        <v>1240</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>1250</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>2010</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>2020</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>2030</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>2040</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>2050</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>2130</v>
       </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1594,7 +1808,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1602,10 +1816,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1613,10 +1827,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9617985E-18ED-4744-B9EC-1780408541FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
   <si>
     <t>Id</t>
   </si>
@@ -168,29 +174,49 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Param1=Rank,Param2=属性</t>
+  </si>
+  <si>
+    <t>Artifact</t>
+  </si>
+  <si>
+    <t>Param1=スキルId</t>
+  </si>
+  <si>
+    <t>金塊</t>
+    <rPh sb="0" eb="2">
+      <t>キンカイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Param1=Nu数</t>
+    <rPh sb="9" eb="10">
+      <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>RandumAddSkill</t>
-  </si>
-  <si>
-    <t>Param1=Rank,Param2=属性</t>
-  </si>
-  <si>
-    <t>Artifact</t>
-  </si>
-  <si>
-    <t>Param1=スキルId</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10(Nu)に換金</t>
+    <rPh sb="7" eb="9">
+      <t>カンキン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,349 +228,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -552,251 +256,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -808,61 +270,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
-    <cellStyle name="入力" xfId="2" builtinId="20"/>
-    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
-    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
-    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
-    <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
-    <cellStyle name="良い" xfId="13" builtinId="26"/>
-    <cellStyle name="警告文" xfId="14" builtinId="11"/>
-    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
-    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
-    <cellStyle name="説明文" xfId="17" builtinId="53"/>
-    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
-    <cellStyle name="出力" xfId="19" builtinId="21"/>
-    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
-    <cellStyle name="計算" xfId="22" builtinId="22"/>
-    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
-    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
-    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="集計" xfId="28" builtinId="25"/>
-    <cellStyle name="悪い" xfId="29" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
-    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
-    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
-    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
-    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1120,16 +538,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1143,7 +561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -1157,7 +575,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1010</v>
       </c>
@@ -1171,7 +589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -1185,7 +603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -1199,7 +617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -1213,7 +631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1050</v>
       </c>
@@ -1227,7 +645,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1100</v>
       </c>
@@ -1241,7 +659,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1110</v>
       </c>
@@ -1255,7 +673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1120</v>
       </c>
@@ -1269,7 +687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1130</v>
       </c>
@@ -1283,7 +701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1140</v>
       </c>
@@ -1297,7 +715,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1150</v>
       </c>
@@ -1311,7 +729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1200</v>
       </c>
@@ -1325,7 +743,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1210</v>
       </c>
@@ -1339,7 +757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1220</v>
       </c>
@@ -1353,7 +771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1230</v>
       </c>
@@ -1367,7 +785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1240</v>
       </c>
@@ -1381,7 +799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1250</v>
       </c>
@@ -1395,7 +813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2010</v>
       </c>
@@ -1409,7 +827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2020</v>
       </c>
@@ -1423,7 +841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -1437,7 +855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2040</v>
       </c>
@@ -1451,7 +869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2050</v>
       </c>
@@ -1465,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2130</v>
       </c>
@@ -1479,44 +897,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="6:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>3010</v>
+      </c>
+      <c r="B26">
+        <v>30</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="6:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="6:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="6:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="6:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="6:6">
+    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="6:6">
+    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" customWidth="1"/>
+    <col min="3" max="3" width="30.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1527,7 +958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -1538,7 +969,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1010</v>
       </c>
@@ -1549,7 +980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -1560,7 +991,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -1571,7 +1002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -1582,7 +1013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1050</v>
       </c>
@@ -1593,7 +1024,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1100</v>
       </c>
@@ -1604,7 +1035,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1110</v>
       </c>
@@ -1615,7 +1046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1120</v>
       </c>
@@ -1626,7 +1057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1130</v>
       </c>
@@ -1637,7 +1068,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1140</v>
       </c>
@@ -1648,7 +1079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1150</v>
       </c>
@@ -1659,7 +1090,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1200</v>
       </c>
@@ -1670,7 +1101,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1210</v>
       </c>
@@ -1681,7 +1112,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1220</v>
       </c>
@@ -1692,7 +1123,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1230</v>
       </c>
@@ -1703,7 +1134,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1240</v>
       </c>
@@ -1714,7 +1145,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1250</v>
       </c>
@@ -1725,7 +1156,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2010</v>
       </c>
@@ -1736,7 +1167,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2020</v>
       </c>
@@ -1747,7 +1178,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2030</v>
       </c>
@@ -1758,7 +1189,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2040</v>
       </c>
@@ -1769,7 +1200,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2050</v>
       </c>
@@ -1780,7 +1211,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2130</v>
       </c>
@@ -1791,50 +1222,71 @@
         <v>43</v>
       </c>
     </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>3010</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.5454545454545" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" t="s">
-        <v>53</v>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9617985E-18ED-4744-B9EC-1780408541FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -22,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
   <si>
     <t>Id</t>
   </si>
@@ -114,40 +108,76 @@
     <t>Rank.Rの闇属性Passive魔法をランダムで入手</t>
   </si>
   <si>
+    <t>虹の指南書</t>
+  </si>
+  <si>
+    <t>Rank.RのActive魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>炎の指南書</t>
+  </si>
+  <si>
+    <t>Rank.Rの炎属性Active魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>雷の指南書</t>
+  </si>
+  <si>
+    <t>Rank.Rの雷属性Active魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>氷の指南書</t>
+  </si>
+  <si>
+    <t>Rank.Rの氷属性Active魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>光の指南書</t>
+  </si>
+  <si>
+    <t>Rank.Rの光属性Active魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>闇の指南書</t>
+  </si>
+  <si>
+    <t>Rank.Rの闇属性Active魔法をランダムで入手</t>
+  </si>
+  <si>
     <t>虹の精霊輝石</t>
   </si>
   <si>
-    <t>Rank.RのActive魔法をランダムで入手</t>
+    <t>Rank.Nの強化魔法をランダムで入手</t>
   </si>
   <si>
     <t>炎の精霊輝石</t>
   </si>
   <si>
-    <t>Rank.Rの炎属性Active魔法をランダムで入手</t>
+    <t>Rank.Nの炎属性強化魔法をランダムで入手</t>
   </si>
   <si>
     <t>雷の精霊輝石</t>
   </si>
   <si>
-    <t>Rank.Rの雷属性Active魔法をランダムで入手</t>
+    <t>Rank.Nの雷属性強化魔法をランダムで入手</t>
   </si>
   <si>
     <t>氷の精霊輝石</t>
   </si>
   <si>
-    <t>Rank.Rの氷属性Active魔法をランダムで入手</t>
+    <t>Rank.Nの氷属性強化魔法をランダムで入手</t>
   </si>
   <si>
     <t>光の精霊輝石</t>
   </si>
   <si>
-    <t>Rank.Rの光属性Active魔法をランダムで入手</t>
+    <t>Rank.Nの光属性強化魔法をランダムで入手</t>
   </si>
   <si>
     <t>闇の精霊輝石</t>
   </si>
   <si>
-    <t>Rank.Rの闇属性Active魔法をランダムで入手</t>
+    <t>Rank.Nの闇属性強化魔法をランダムで入手</t>
   </si>
   <si>
     <t>妖精の祈り</t>
@@ -171,9 +201,24 @@
     <t>ヒールユニット</t>
   </si>
   <si>
+    <t>金塊</t>
+  </si>
+  <si>
+    <t>10(Nu)に換金</t>
+  </si>
+  <si>
+    <t>ダイアモンド</t>
+  </si>
+  <si>
+    <t>20(Nu)に換金</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
+    <t>RandumAddSkill</t>
+  </si>
+  <si>
     <t>Param1=Rank,Param2=属性</t>
   </si>
   <si>
@@ -183,40 +228,23 @@
     <t>Param1=スキルId</t>
   </si>
   <si>
-    <t>金塊</t>
-    <rPh sb="0" eb="2">
-      <t>キンカイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Currency</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Param1=Nu数</t>
-    <rPh sb="9" eb="10">
-      <t>カズ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>RandumAddSkill</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>10(Nu)に換金</t>
-    <rPh sb="7" eb="9">
-      <t>カンキン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,27 +256,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -256,9 +606,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -270,17 +862,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -538,16 +1174,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -561,7 +1197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -575,7 +1211,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1010</v>
       </c>
@@ -589,7 +1225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -603,7 +1239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -617,7 +1253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -631,7 +1267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>1050</v>
       </c>
@@ -645,7 +1281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>1100</v>
       </c>
@@ -659,7 +1295,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>1110</v>
       </c>
@@ -673,7 +1309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>1120</v>
       </c>
@@ -687,7 +1323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>1130</v>
       </c>
@@ -701,7 +1337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>1140</v>
       </c>
@@ -715,7 +1351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>1150</v>
       </c>
@@ -729,7 +1365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>1200</v>
       </c>
@@ -743,7 +1379,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>1210</v>
       </c>
@@ -757,7 +1393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>1220</v>
       </c>
@@ -771,7 +1407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>1230</v>
       </c>
@@ -785,7 +1421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>1240</v>
       </c>
@@ -799,7 +1435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>1250</v>
       </c>
@@ -813,141 +1449,240 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4">
       <c r="A20">
+        <v>1300</v>
+      </c>
+      <c r="B20">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>110</v>
+      </c>
+      <c r="D20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>1310</v>
+      </c>
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>110</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>1320</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>110</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>1330</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>110</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>1340</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>110</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>1350</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>110</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
         <v>2010</v>
       </c>
-      <c r="B20">
+      <c r="B26">
         <v>20</v>
       </c>
-      <c r="C20">
+      <c r="C26">
         <v>310010</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2020</v>
-      </c>
-      <c r="B21">
-        <v>20</v>
-      </c>
-      <c r="C21">
-        <v>310020</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2030</v>
-      </c>
-      <c r="B22">
-        <v>20</v>
-      </c>
-      <c r="C22">
-        <v>310030</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2040</v>
-      </c>
-      <c r="B23">
-        <v>20</v>
-      </c>
-      <c r="C23">
-        <v>310040</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2050</v>
-      </c>
-      <c r="B24">
-        <v>20</v>
-      </c>
-      <c r="C24">
-        <v>310050</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2130</v>
-      </c>
-      <c r="B25">
-        <v>20</v>
-      </c>
-      <c r="C25">
-        <v>310130</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>3010</v>
-      </c>
-      <c r="B26">
-        <v>30</v>
-      </c>
-      <c r="C26">
-        <v>10</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F29" s="1"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>2020</v>
+      </c>
+      <c r="B27">
+        <v>20</v>
+      </c>
+      <c r="C27">
+        <v>310020</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>2030</v>
+      </c>
+      <c r="B28">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>310030</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29">
+        <v>2040</v>
+      </c>
+      <c r="B29">
+        <v>20</v>
+      </c>
+      <c r="C29">
+        <v>310040</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30">
+        <v>2050</v>
+      </c>
+      <c r="B30">
+        <v>20</v>
+      </c>
+      <c r="C30">
+        <v>310050</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31">
+        <v>2130</v>
+      </c>
+      <c r="B31">
+        <v>20</v>
+      </c>
+      <c r="C31">
+        <v>310130</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>3010</v>
+      </c>
+      <c r="B32">
+        <v>30</v>
+      </c>
+      <c r="C32">
+        <v>10</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33">
+        <v>3020</v>
+      </c>
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="6:6">
       <c r="F34" s="1"/>
     </row>
+    <row r="35" spans="6:6">
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="6:6">
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="6:6">
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="6:6">
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="6:6">
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="6:6">
+      <c r="F40" s="1"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="13.7265625" customWidth="1"/>
-    <col min="3" max="3" width="30.08984375" customWidth="1"/>
+    <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
+    <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -958,7 +1693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -969,7 +1704,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1010</v>
       </c>
@@ -980,7 +1715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -991,7 +1726,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -1002,7 +1737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -1013,7 +1748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>1050</v>
       </c>
@@ -1024,7 +1759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>1100</v>
       </c>
@@ -1035,7 +1770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>1110</v>
       </c>
@@ -1046,7 +1781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>1120</v>
       </c>
@@ -1057,7 +1792,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>1130</v>
       </c>
@@ -1068,7 +1803,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>1140</v>
       </c>
@@ -1079,7 +1814,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>1150</v>
       </c>
@@ -1090,7 +1825,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>1200</v>
       </c>
@@ -1101,7 +1836,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>1210</v>
       </c>
@@ -1112,7 +1847,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>1220</v>
       </c>
@@ -1123,7 +1858,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>1230</v>
       </c>
@@ -1134,7 +1869,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>1240</v>
       </c>
@@ -1145,7 +1880,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>1250</v>
       </c>
@@ -1156,9 +1891,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20">
-        <v>2010</v>
+        <v>1300</v>
       </c>
       <c r="B20" t="s">
         <v>42</v>
@@ -1167,126 +1902,204 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21">
-        <v>2020</v>
+        <v>1310</v>
       </c>
       <c r="B21" t="s">
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
+        <v>1320</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>1330</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>1340</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>1350</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>2010</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>2020</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>2030</v>
       </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
         <v>2040</v>
       </c>
-      <c r="B23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
         <v>2050</v>
       </c>
-      <c r="B24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>2130</v>
       </c>
-      <c r="B25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
         <v>3010</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>57</v>
+      <c r="B32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>3020</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="2" max="2" width="15.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -30,6 +30,9 @@
     <t>Param2</t>
   </si>
   <si>
+    <t>Param3</t>
+  </si>
+  <si>
     <t>Text</t>
   </si>
   <si>
@@ -211,6 +214,13 @@
   </si>
   <si>
     <t>20(Nu)に換金</t>
+  </si>
+  <si>
+    <t>初級指南書</t>
+  </si>
+  <si>
+    <t>Expを50入手する
+Lvが10以下の場合、取得経験値が2倍になる</t>
   </si>
   <si>
     <t>Type</t>
@@ -239,10 +249,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -261,6 +271,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -269,7 +286,36 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,29 +331,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,6 +365,13 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -336,43 +390,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -382,25 +399,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -413,19 +423,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -437,163 +603,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,6 +614,32 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -622,11 +658,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,43 +706,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -712,154 +722,157 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1183,7 +1196,7 @@
   <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1196,8 +1209,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -1210,8 +1226,11 @@
       <c r="D2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1010</v>
       </c>
@@ -1224,8 +1243,11 @@
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -1238,8 +1260,11 @@
       <c r="D4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -1252,8 +1277,11 @@
       <c r="D5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -1266,8 +1294,11 @@
       <c r="D6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1050</v>
       </c>
@@ -1280,8 +1311,11 @@
       <c r="D7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1100</v>
       </c>
@@ -1294,8 +1328,11 @@
       <c r="D8">
         <v>-1</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1110</v>
       </c>
@@ -1308,8 +1345,11 @@
       <c r="D9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1120</v>
       </c>
@@ -1322,8 +1362,11 @@
       <c r="D10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1130</v>
       </c>
@@ -1336,8 +1379,11 @@
       <c r="D11">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1140</v>
       </c>
@@ -1350,8 +1396,11 @@
       <c r="D12">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1150</v>
       </c>
@@ -1364,8 +1413,11 @@
       <c r="D13">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1200</v>
       </c>
@@ -1378,8 +1430,11 @@
       <c r="D14">
         <v>-1</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1210</v>
       </c>
@@ -1392,8 +1447,11 @@
       <c r="D15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>1220</v>
       </c>
@@ -1406,8 +1464,11 @@
       <c r="D16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>1230</v>
       </c>
@@ -1420,8 +1481,11 @@
       <c r="D17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>1240</v>
       </c>
@@ -1434,8 +1498,11 @@
       <c r="D18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>1250</v>
       </c>
@@ -1448,8 +1515,11 @@
       <c r="D19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>1300</v>
       </c>
@@ -1462,8 +1532,11 @@
       <c r="D20">
         <v>-1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>1310</v>
       </c>
@@ -1476,8 +1549,11 @@
       <c r="D21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>1320</v>
       </c>
@@ -1490,8 +1566,11 @@
       <c r="D22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>1330</v>
       </c>
@@ -1504,8 +1583,11 @@
       <c r="D23">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>1340</v>
       </c>
@@ -1518,8 +1600,11 @@
       <c r="D24">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>1350</v>
       </c>
@@ -1532,8 +1617,11 @@
       <c r="D25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>2010</v>
       </c>
@@ -1546,8 +1634,11 @@
       <c r="D26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>2020</v>
       </c>
@@ -1560,8 +1651,11 @@
       <c r="D27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>2030</v>
       </c>
@@ -1574,8 +1668,11 @@
       <c r="D28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>2040</v>
       </c>
@@ -1588,8 +1685,11 @@
       <c r="D29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>2050</v>
       </c>
@@ -1602,8 +1702,11 @@
       <c r="D30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>2130</v>
       </c>
@@ -1616,8 +1719,11 @@
       <c r="D31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>3010</v>
       </c>
@@ -1630,8 +1736,11 @@
       <c r="D32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>3020</v>
       </c>
@@ -1644,8 +1753,26 @@
       <c r="D33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="6:6">
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>4010</v>
+      </c>
+      <c r="B34">
+        <v>40</v>
+      </c>
+      <c r="C34">
+        <v>10</v>
+      </c>
+      <c r="D34">
+        <v>50</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="6:6">
@@ -1675,7 +1802,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -1687,10 +1814,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1698,10 +1825,10 @@
         <v>1000</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1709,10 +1836,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1720,10 +1847,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1731,10 +1858,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1742,10 +1869,10 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1753,10 +1880,10 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1764,10 +1891,10 @@
         <v>1100</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1775,10 +1902,10 @@
         <v>1110</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1786,10 +1913,10 @@
         <v>1120</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1797,10 +1924,10 @@
         <v>1130</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1808,10 +1935,10 @@
         <v>1140</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1819,10 +1946,10 @@
         <v>1150</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1830,10 +1957,10 @@
         <v>1200</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1841,10 +1968,10 @@
         <v>1210</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1852,10 +1979,10 @@
         <v>1220</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1863,10 +1990,10 @@
         <v>1230</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1874,10 +2001,10 @@
         <v>1240</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1885,10 +2012,10 @@
         <v>1250</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1896,10 +2023,10 @@
         <v>1300</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1907,10 +2034,10 @@
         <v>1310</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1918,10 +2045,10 @@
         <v>1320</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1929,10 +2056,10 @@
         <v>1330</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1940,10 +2067,10 @@
         <v>1340</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1951,10 +2078,10 @@
         <v>1350</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1962,10 +2089,10 @@
         <v>2010</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1973,10 +2100,10 @@
         <v>2020</v>
       </c>
       <c r="B27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" t="s">
         <v>56</v>
-      </c>
-      <c r="C27" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1984,10 +2111,10 @@
         <v>2030</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1995,10 +2122,10 @@
         <v>2040</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2006,10 +2133,10 @@
         <v>2050</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2017,10 +2144,10 @@
         <v>2130</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2028,10 +2155,10 @@
         <v>3010</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2039,10 +2166,21 @@
         <v>3020</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" ht="39" spans="1:3">
+      <c r="A34">
+        <v>4010</v>
+      </c>
+      <c r="B34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2062,7 +2200,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2070,10 +2208,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2081,10 +2219,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2092,10 +2230,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="81">
   <si>
     <t>Id</t>
   </si>
@@ -221,6 +221,27 @@
   <si>
     <t>Expを50入手する
 Lvが10以下の場合、取得経験値が2倍になる</t>
+  </si>
+  <si>
+    <t>中級指南書</t>
+  </si>
+  <si>
+    <t>Expを50入手する
+Lvが20以下の場合、取得経験値が2倍になる</t>
+  </si>
+  <si>
+    <t>上級指南書</t>
+  </si>
+  <si>
+    <t>Expを50入手する
+Lvが30以下の場合、取得経験値が2倍になる</t>
+  </si>
+  <si>
+    <t>特級指南書</t>
+  </si>
+  <si>
+    <t>Expを50入手する
+Lvが40以下の場合、取得経験値が2倍になる</t>
   </si>
   <si>
     <t>Type</t>
@@ -249,10 +270,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -284,9 +305,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,14 +315,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,6 +323,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,45 +353,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -377,7 +361,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -399,6 +390,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -407,12 +406,34 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -423,187 +444,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,27 +638,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -654,6 +664,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -676,30 +701,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -714,6 +715,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -722,145 +743,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1775,13 +1796,58 @@
       </c>
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="6:6">
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>4020</v>
+      </c>
+      <c r="B35">
+        <v>40</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+      <c r="D35">
+        <v>50</v>
+      </c>
+      <c r="E35">
+        <v>20</v>
+      </c>
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="6:6">
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>4030</v>
+      </c>
+      <c r="B36">
+        <v>40</v>
+      </c>
+      <c r="C36">
+        <v>10</v>
+      </c>
+      <c r="D36">
+        <v>50</v>
+      </c>
+      <c r="E36">
+        <v>30</v>
+      </c>
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="6:6">
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>4040</v>
+      </c>
+      <c r="B37">
+        <v>40</v>
+      </c>
+      <c r="C37">
+        <v>10</v>
+      </c>
+      <c r="D37">
+        <v>50</v>
+      </c>
+      <c r="E37">
+        <v>40</v>
+      </c>
       <c r="F37" s="1"/>
     </row>
     <row r="38" spans="6:6">
@@ -1802,7 +1868,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -2181,6 +2247,39 @@
       </c>
       <c r="C34" s="2" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="35" ht="39" spans="1:3">
+      <c r="A35">
+        <v>4020</v>
+      </c>
+      <c r="B35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" ht="39" spans="1:3">
+      <c r="A36">
+        <v>4030</v>
+      </c>
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" ht="39" spans="1:3">
+      <c r="A37">
+        <v>4040</v>
+      </c>
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2200,7 +2299,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2208,10 +2307,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2219,10 +2318,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2230,10 +2329,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
   <si>
     <t>Id</t>
   </si>
@@ -242,6 +242,66 @@
   <si>
     <t>Expを50入手する
 Lvが40以下の場合、取得経験値が2倍になる</t>
+  </si>
+  <si>
+    <t>レッドスピネル</t>
+  </si>
+  <si>
+    <t>炎属性の適正アップ</t>
+  </si>
+  <si>
+    <t>シトリン</t>
+  </si>
+  <si>
+    <t>雷属性の適正アップ</t>
+  </si>
+  <si>
+    <t>タンザナイト</t>
+  </si>
+  <si>
+    <t>氷属性の適正アップ</t>
+  </si>
+  <si>
+    <t>ムーンストーン</t>
+  </si>
+  <si>
+    <t>光属性の適正アップ</t>
+  </si>
+  <si>
+    <t>ブラッドストーン</t>
+  </si>
+  <si>
+    <t>闇属性の適正アップ</t>
+  </si>
+  <si>
+    <t>生命の雫</t>
+  </si>
+  <si>
+    <t>最大Hpを1アップ</t>
+  </si>
+  <si>
+    <t>活力の果実</t>
+  </si>
+  <si>
+    <t>最大Cpを１アップ</t>
+  </si>
+  <si>
+    <t>力のたすき</t>
+  </si>
+  <si>
+    <t>Atkを１アップ</t>
+  </si>
+  <si>
+    <t>守りのお守り</t>
+  </si>
+  <si>
+    <t>Defを１アップ</t>
+  </si>
+  <si>
+    <t>妖精の羽</t>
+  </si>
+  <si>
+    <t>Spdを１アップ</t>
   </si>
   <si>
     <t>Type</t>
@@ -270,8 +330,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -291,15 +351,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,24 +421,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -338,22 +460,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -367,57 +473,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -444,187 +504,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,17 +698,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,16 +733,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -698,20 +763,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -727,11 +789,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -743,7 +803,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -752,7 +812,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -761,127 +821,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1214,7 +1274,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1850,14 +1910,178 @@
       </c>
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:6">
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>4110</v>
+      </c>
+      <c r="B38">
+        <v>40</v>
+      </c>
+      <c r="C38">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:6">
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>4120</v>
+      </c>
+      <c r="B39">
+        <v>40</v>
+      </c>
+      <c r="C39">
+        <v>20</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:6">
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>4130</v>
+      </c>
+      <c r="B40">
+        <v>40</v>
+      </c>
+      <c r="C40">
+        <v>20</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
       <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>4140</v>
+      </c>
+      <c r="B41">
+        <v>40</v>
+      </c>
+      <c r="C41">
+        <v>20</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>4150</v>
+      </c>
+      <c r="B42">
+        <v>40</v>
+      </c>
+      <c r="C42">
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>4210</v>
+      </c>
+      <c r="B43">
+        <v>40</v>
+      </c>
+      <c r="C43">
+        <v>30</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>4220</v>
+      </c>
+      <c r="B44">
+        <v>40</v>
+      </c>
+      <c r="C44">
+        <v>30</v>
+      </c>
+      <c r="D44">
+        <v>6</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>4230</v>
+      </c>
+      <c r="B45">
+        <v>40</v>
+      </c>
+      <c r="C45">
+        <v>30</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>4240</v>
+      </c>
+      <c r="B46">
+        <v>40</v>
+      </c>
+      <c r="C46">
+        <v>30</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>4250</v>
+      </c>
+      <c r="B47">
+        <v>40</v>
+      </c>
+      <c r="C47">
+        <v>30</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1868,7 +2092,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -2280,6 +2504,116 @@
       </c>
       <c r="C37" s="2" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>4110</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>4120</v>
+      </c>
+      <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>4130</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>4140</v>
+      </c>
+      <c r="B41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>4150</v>
+      </c>
+      <c r="B42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>4210</v>
+      </c>
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>4220</v>
+      </c>
+      <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>4230</v>
+      </c>
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>4240</v>
+      </c>
+      <c r="B46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>4250</v>
+      </c>
+      <c r="B47" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2299,7 +2633,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2307,10 +2641,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2318,10 +2652,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2329,10 +2663,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
     <t>妖精の祈り</t>
   </si>
   <si>
-    <t>評価値+5</t>
+    <t>信仰度+5</t>
   </si>
   <si>
     <t>月のかけら</t>
@@ -207,13 +207,13 @@
     <t>金塊</t>
   </si>
   <si>
-    <t>10(Nu)に換金</t>
+    <t>10(Nu)に換金できる</t>
   </si>
   <si>
     <t>ダイアモンド</t>
   </si>
   <si>
-    <t>20(Nu)に換金</t>
+    <t>20(Nu)に換金できる</t>
   </si>
   <si>
     <t>初級指南書</t>
@@ -330,9 +330,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -351,47 +351,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -407,15 +369,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -428,8 +389,77 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -444,40 +474,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -504,13 +504,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,13 +612,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -540,43 +660,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -588,103 +684,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -709,15 +709,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -734,21 +725,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -759,21 +735,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -795,6 +756,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -803,7 +803,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -812,7 +812,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -821,127 +821,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -330,9 +330,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -351,9 +351,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -367,7 +381,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -376,16 +389,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -394,21 +408,6 @@
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -434,14 +433,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -449,24 +440,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -481,21 +464,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -504,25 +504,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -534,127 +678,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -666,25 +690,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,13 +704,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -720,6 +730,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -742,8 +761,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -751,8 +770,19 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -771,30 +801,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -803,40 +809,40 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -845,107 +851,107 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -954,6 +960,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1601,104 +1610,104 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20">
+      <c r="A20" s="3">
         <v>1300</v>
       </c>
-      <c r="B20">
-        <v>10</v>
-      </c>
-      <c r="C20">
+      <c r="B20" s="3">
+        <v>11</v>
+      </c>
+      <c r="C20" s="3">
         <v>110</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="3">
         <v>-1</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21">
+      <c r="A21" s="3">
         <v>1310</v>
       </c>
-      <c r="B21">
-        <v>10</v>
-      </c>
-      <c r="C21">
+      <c r="B21" s="3">
+        <v>11</v>
+      </c>
+      <c r="C21" s="3">
         <v>110</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="3">
         <v>1</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22">
+      <c r="A22" s="3">
         <v>1320</v>
       </c>
-      <c r="B22">
-        <v>10</v>
-      </c>
-      <c r="C22">
+      <c r="B22" s="3">
+        <v>11</v>
+      </c>
+      <c r="C22" s="3">
         <v>110</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="3">
         <v>2</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23">
+      <c r="A23" s="3">
         <v>1330</v>
       </c>
-      <c r="B23">
-        <v>10</v>
-      </c>
-      <c r="C23">
+      <c r="B23" s="3">
+        <v>11</v>
+      </c>
+      <c r="C23" s="3">
         <v>110</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="3">
         <v>3</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24">
+      <c r="A24" s="3">
         <v>1340</v>
       </c>
-      <c r="B24">
-        <v>10</v>
-      </c>
-      <c r="C24">
+      <c r="B24" s="3">
+        <v>11</v>
+      </c>
+      <c r="C24" s="3">
         <v>110</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="3">
         <v>4</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25">
+      <c r="A25" s="3">
         <v>1350</v>
       </c>
-      <c r="B25">
-        <v>10</v>
-      </c>
-      <c r="C25">
+      <c r="B25" s="3">
+        <v>11</v>
+      </c>
+      <c r="C25" s="3">
         <v>110</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="3">
         <v>5</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
     <t>月のかけら</t>
   </si>
   <si>
-    <t>錬金術師の遺稿</t>
+    <t>商売の才覚書</t>
   </si>
   <si>
     <t xml:space="preserve">ワタリガラスの旗 </t>
@@ -332,8 +332,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -348,50 +348,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -411,8 +367,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -426,23 +435,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -458,7 +459,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -466,23 +482,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -522,175 +522,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -704,17 +704,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -737,8 +731,38 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -754,15 +778,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -786,21 +801,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -809,16 +809,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -827,127 +827,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,9 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="102">
   <si>
     <t>Id</t>
+  </si>
+  <si>
+    <t>IconIndex</t>
   </si>
   <si>
     <t>ItemType</t>
@@ -330,9 +333,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -351,8 +354,76 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -368,17 +439,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -391,90 +455,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -489,7 +470,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -510,6 +513,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -522,175 +567,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,39 +704,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -768,6 +738,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -784,15 +778,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -801,6 +786,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -809,145 +812,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1283,10 +1286,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1302,314 +1305,371 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1000</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
       <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
         <v>-1</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1010</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>1020</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1030</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>1040</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
         <v>4</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>1050</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>1100</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
         <v>20</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>-1</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>1110</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
         <v>20</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>1120</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
         <v>20</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>2</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>1130</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
         <v>20</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>3</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>1140</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
         <v>20</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>4</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>1150</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
         <v>20</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>5</v>
       </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>1200</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
         <v>2</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>-1</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>1210</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
         <v>2</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>1</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>1220</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>1230</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
         <v>2</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>3</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>1240</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="D18">
         <v>2</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>4</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>1250</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
         <v>2</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>5</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="3">
         <v>1300</v>
       </c>
@@ -1617,16 +1677,19 @@
         <v>11</v>
       </c>
       <c r="C20" s="3">
+        <v>11</v>
+      </c>
+      <c r="D20" s="3">
         <v>110</v>
       </c>
-      <c r="D20" s="3">
+      <c r="E20" s="3">
         <v>-1</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="3">
         <v>1310</v>
       </c>
@@ -1634,16 +1697,19 @@
         <v>11</v>
       </c>
       <c r="C21" s="3">
+        <v>11</v>
+      </c>
+      <c r="D21" s="3">
         <v>110</v>
       </c>
-      <c r="D21" s="3">
+      <c r="E21" s="3">
         <v>1</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="3">
         <v>1320</v>
       </c>
@@ -1651,16 +1717,19 @@
         <v>11</v>
       </c>
       <c r="C22" s="3">
+        <v>11</v>
+      </c>
+      <c r="D22" s="3">
         <v>110</v>
       </c>
-      <c r="D22" s="3">
+      <c r="E22" s="3">
         <v>2</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="3">
         <v>1330</v>
       </c>
@@ -1668,16 +1737,19 @@
         <v>11</v>
       </c>
       <c r="C23" s="3">
+        <v>11</v>
+      </c>
+      <c r="D23" s="3">
         <v>110</v>
       </c>
-      <c r="D23" s="3">
+      <c r="E23" s="3">
         <v>3</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="3">
         <v>1340</v>
       </c>
@@ -1685,16 +1757,19 @@
         <v>11</v>
       </c>
       <c r="C24" s="3">
+        <v>11</v>
+      </c>
+      <c r="D24" s="3">
         <v>110</v>
       </c>
-      <c r="D24" s="3">
+      <c r="E24" s="3">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="3">
         <v>1350</v>
       </c>
@@ -1702,393 +1777,462 @@
         <v>11</v>
       </c>
       <c r="C25" s="3">
+        <v>11</v>
+      </c>
+      <c r="D25" s="3">
         <v>110</v>
       </c>
-      <c r="D25" s="3">
+      <c r="E25" s="3">
         <v>5</v>
       </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>2010</v>
       </c>
       <c r="B26">
+        <v>58</v>
+      </c>
+      <c r="C26">
         <v>20</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>310010</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
       <c r="E26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>2020</v>
       </c>
       <c r="B27">
+        <v>58</v>
+      </c>
+      <c r="C27">
         <v>20</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>310020</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
       <c r="E27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>2030</v>
       </c>
       <c r="B28">
+        <v>58</v>
+      </c>
+      <c r="C28">
         <v>20</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>310030</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
       <c r="E28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>2040</v>
       </c>
       <c r="B29">
+        <v>58</v>
+      </c>
+      <c r="C29">
         <v>20</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>310040</v>
       </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
       <c r="E29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>2050</v>
       </c>
       <c r="B30">
+        <v>58</v>
+      </c>
+      <c r="C30">
         <v>20</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>310050</v>
       </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
       <c r="E30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>2130</v>
       </c>
       <c r="B31">
+        <v>58</v>
+      </c>
+      <c r="C31">
         <v>20</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>310130</v>
       </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
       <c r="E31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>3010</v>
       </c>
       <c r="B32">
+        <v>231</v>
+      </c>
+      <c r="C32">
         <v>30</v>
       </c>
-      <c r="C32">
-        <v>10</v>
-      </c>
       <c r="D32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>3020</v>
       </c>
       <c r="B33">
+        <v>231</v>
+      </c>
+      <c r="C33">
         <v>30</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>20</v>
       </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
       <c r="E33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>4010</v>
       </c>
       <c r="B34">
+        <v>220</v>
+      </c>
+      <c r="C34">
         <v>40</v>
       </c>
-      <c r="C34">
-        <v>10</v>
-      </c>
       <c r="D34">
+        <v>10</v>
+      </c>
+      <c r="E34">
         <v>50</v>
       </c>
-      <c r="E34">
-        <v>10</v>
-      </c>
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="F34">
+        <v>10</v>
+      </c>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>4020</v>
       </c>
       <c r="B35">
+        <v>220</v>
+      </c>
+      <c r="C35">
         <v>40</v>
       </c>
-      <c r="C35">
-        <v>10</v>
-      </c>
       <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35">
         <v>50</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>20</v>
       </c>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>4030</v>
       </c>
       <c r="B36">
+        <v>220</v>
+      </c>
+      <c r="C36">
         <v>40</v>
       </c>
-      <c r="C36">
-        <v>10</v>
-      </c>
       <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="E36">
         <v>50</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>30</v>
       </c>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>4040</v>
       </c>
       <c r="B37">
+        <v>220</v>
+      </c>
+      <c r="C37">
         <v>40</v>
       </c>
-      <c r="C37">
-        <v>10</v>
-      </c>
       <c r="D37">
+        <v>10</v>
+      </c>
+      <c r="E37">
         <v>50</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>40</v>
       </c>
-      <c r="F37" s="1"/>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>4110</v>
       </c>
       <c r="B38">
+        <v>224</v>
+      </c>
+      <c r="C38">
         <v>40</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>20</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
-      <c r="F38" s="1"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4120</v>
       </c>
       <c r="B39">
+        <v>224</v>
+      </c>
+      <c r="C39">
         <v>40</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>20</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>2</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>1</v>
       </c>
-      <c r="F39" s="1"/>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4130</v>
       </c>
       <c r="B40">
+        <v>224</v>
+      </c>
+      <c r="C40">
         <v>40</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>20</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>3</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>1</v>
       </c>
-      <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>4140</v>
       </c>
       <c r="B41">
+        <v>224</v>
+      </c>
+      <c r="C41">
         <v>40</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>20</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>4</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>4150</v>
       </c>
       <c r="B42">
+        <v>224</v>
+      </c>
+      <c r="C42">
         <v>40</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>20</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>5</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>4210</v>
       </c>
       <c r="B43">
+        <v>204</v>
+      </c>
+      <c r="C43">
         <v>40</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>30</v>
       </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
       <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>4220</v>
       </c>
       <c r="B44">
+        <v>202</v>
+      </c>
+      <c r="C44">
         <v>40</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>30</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>6</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>4230</v>
       </c>
       <c r="B45">
+        <v>117</v>
+      </c>
+      <c r="C45">
         <v>40</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>30</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>4240</v>
       </c>
       <c r="B46">
+        <v>115</v>
+      </c>
+      <c r="C46">
         <v>40</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>30</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>2</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>4250</v>
       </c>
       <c r="B47">
+        <v>171</v>
+      </c>
+      <c r="C47">
         <v>40</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>30</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>3</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>1</v>
       </c>
     </row>
@@ -2113,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2124,10 +2268,10 @@
         <v>1000</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2135,10 +2279,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2146,10 +2290,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2157,10 +2301,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2168,10 +2312,10 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2179,10 +2323,10 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2190,10 +2334,10 @@
         <v>1100</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2201,10 +2345,10 @@
         <v>1110</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2212,10 +2356,10 @@
         <v>1120</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2223,10 +2367,10 @@
         <v>1130</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2234,10 +2378,10 @@
         <v>1140</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2245,10 +2389,10 @@
         <v>1150</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2256,10 +2400,10 @@
         <v>1200</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2267,10 +2411,10 @@
         <v>1210</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2278,10 +2422,10 @@
         <v>1220</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2289,10 +2433,10 @@
         <v>1230</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2300,10 +2444,10 @@
         <v>1240</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2311,10 +2455,10 @@
         <v>1250</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2322,10 +2466,10 @@
         <v>1300</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2333,10 +2477,10 @@
         <v>1310</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2344,10 +2488,10 @@
         <v>1320</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2355,10 +2499,10 @@
         <v>1330</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2366,10 +2510,10 @@
         <v>1340</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2377,10 +2521,10 @@
         <v>1350</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2388,10 +2532,10 @@
         <v>2010</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2399,10 +2543,10 @@
         <v>2020</v>
       </c>
       <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
         <v>57</v>
-      </c>
-      <c r="C27" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2410,10 +2554,10 @@
         <v>2030</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2421,10 +2565,10 @@
         <v>2040</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2432,10 +2576,10 @@
         <v>2050</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2443,10 +2587,10 @@
         <v>2130</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2454,10 +2598,10 @@
         <v>3010</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2465,10 +2609,10 @@
         <v>3020</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" ht="39" spans="1:3">
@@ -2476,10 +2620,10 @@
         <v>4010</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" ht="39" spans="1:3">
@@ -2487,10 +2631,10 @@
         <v>4020</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" ht="39" spans="1:3">
@@ -2498,10 +2642,10 @@
         <v>4030</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" ht="39" spans="1:3">
@@ -2509,10 +2653,10 @@
         <v>4040</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2520,10 +2664,10 @@
         <v>4110</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2531,10 +2675,10 @@
         <v>4120</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2542,10 +2686,10 @@
         <v>4130</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2553,10 +2697,10 @@
         <v>4140</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2564,10 +2708,10 @@
         <v>4150</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2575,10 +2719,10 @@
         <v>4210</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2586,10 +2730,10 @@
         <v>4220</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2597,10 +2741,10 @@
         <v>4230</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2608,10 +2752,10 @@
         <v>4240</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -2619,10 +2763,10 @@
         <v>4250</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2642,7 +2786,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2650,10 +2794,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2661,10 +2805,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2672,10 +2816,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
   <si>
     <t>Id</t>
   </si>
@@ -202,6 +202,15 @@
   </si>
   <si>
     <t>先陣の心得</t>
+  </si>
+  <si>
+    <t>ヒスイの勾玉</t>
+  </si>
+  <si>
+    <t>英傑の盾</t>
+  </si>
+  <si>
+    <t>鷹の目</t>
   </si>
   <si>
     <t>ヒールユニット</t>
@@ -354,8 +363,68 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,8 +437,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -377,7 +470,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -391,64 +484,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -463,35 +501,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -513,187 +522,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -723,21 +732,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -757,6 +751,24 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -787,20 +799,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -812,7 +821,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -821,7 +830,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -830,127 +839,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1286,7 +1295,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1891,7 +1900,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>2130</v>
+        <v>2060</v>
       </c>
       <c r="B31">
         <v>58</v>
@@ -1900,7 +1909,7 @@
         <v>20</v>
       </c>
       <c r="D31">
-        <v>310130</v>
+        <v>310060</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1911,16 +1920,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>3010</v>
+        <v>2070</v>
       </c>
       <c r="B32">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="C32">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>310070</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1931,90 +1940,87 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
+        <v>2080</v>
+      </c>
+      <c r="B33">
+        <v>58</v>
+      </c>
+      <c r="C33">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>310070</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>2130</v>
+      </c>
+      <c r="B34">
+        <v>58</v>
+      </c>
+      <c r="C34">
+        <v>20</v>
+      </c>
+      <c r="D34">
+        <v>310130</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>3010</v>
+      </c>
+      <c r="B35">
+        <v>231</v>
+      </c>
+      <c r="C35">
+        <v>30</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
         <v>3020</v>
       </c>
-      <c r="B33">
+      <c r="B36">
         <v>231</v>
       </c>
-      <c r="C33">
+      <c r="C36">
         <v>30</v>
       </c>
-      <c r="D33">
+      <c r="D36">
         <v>20</v>
       </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>4010</v>
-      </c>
-      <c r="B34">
-        <v>220</v>
-      </c>
-      <c r="C34">
-        <v>40</v>
-      </c>
-      <c r="D34">
-        <v>10</v>
-      </c>
-      <c r="E34">
-        <v>50</v>
-      </c>
-      <c r="F34">
-        <v>10</v>
-      </c>
-      <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>4020</v>
-      </c>
-      <c r="B35">
-        <v>220</v>
-      </c>
-      <c r="C35">
-        <v>40</v>
-      </c>
-      <c r="D35">
-        <v>10</v>
-      </c>
-      <c r="E35">
-        <v>50</v>
-      </c>
-      <c r="F35">
-        <v>20</v>
-      </c>
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>4030</v>
-      </c>
-      <c r="B36">
-        <v>220</v>
-      </c>
-      <c r="C36">
-        <v>40</v>
-      </c>
-      <c r="D36">
-        <v>10</v>
-      </c>
       <c r="E36">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>30</v>
-      </c>
-      <c r="G36" s="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>4040</v>
+        <v>4010</v>
       </c>
       <c r="B37">
         <v>220</v>
@@ -2029,76 +2035,76 @@
         <v>50</v>
       </c>
       <c r="F37">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>4110</v>
+        <v>4020</v>
       </c>
       <c r="B38">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C38">
         <v>40</v>
       </c>
       <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38">
+        <v>50</v>
+      </c>
+      <c r="F38">
         <v>20</v>
-      </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
       </c>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>4120</v>
+        <v>4030</v>
       </c>
       <c r="B39">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C39">
         <v>40</v>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>4130</v>
+        <v>4040</v>
       </c>
       <c r="B40">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C40">
         <v>40</v>
       </c>
       <c r="D40">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:7">
       <c r="A41">
-        <v>4140</v>
+        <v>4110</v>
       </c>
       <c r="B41">
         <v>224</v>
@@ -2110,15 +2116,16 @@
         <v>20</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
-        <v>4150</v>
+        <v>4120</v>
       </c>
       <c r="B42">
         <v>224</v>
@@ -2130,47 +2137,49 @@
         <v>20</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
-        <v>4210</v>
+        <v>4130</v>
       </c>
       <c r="B43">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C43">
         <v>40</v>
       </c>
       <c r="D43">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>4220</v>
+        <v>4140</v>
       </c>
       <c r="B44">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C44">
         <v>40</v>
       </c>
       <c r="D44">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -2178,19 +2187,19 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>4230</v>
+        <v>4150</v>
       </c>
       <c r="B45">
-        <v>117</v>
+        <v>224</v>
       </c>
       <c r="C45">
         <v>40</v>
       </c>
       <c r="D45">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -2198,10 +2207,10 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>4240</v>
+        <v>4210</v>
       </c>
       <c r="B46">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="C46">
         <v>40</v>
@@ -2210,7 +2219,7 @@
         <v>30</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -2218,10 +2227,10 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>4250</v>
+        <v>4220</v>
       </c>
       <c r="B47">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="C47">
         <v>40</v>
@@ -2230,9 +2239,69 @@
         <v>30</v>
       </c>
       <c r="E47">
+        <v>6</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>4230</v>
+      </c>
+      <c r="B48">
+        <v>117</v>
+      </c>
+      <c r="C48">
+        <v>40</v>
+      </c>
+      <c r="D48">
+        <v>30</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>4240</v>
+      </c>
+      <c r="B49">
+        <v>115</v>
+      </c>
+      <c r="C49">
+        <v>40</v>
+      </c>
+      <c r="D49">
+        <v>30</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>4250</v>
+      </c>
+      <c r="B50">
+        <v>171</v>
+      </c>
+      <c r="C50">
+        <v>40</v>
+      </c>
+      <c r="D50">
+        <v>30</v>
+      </c>
+      <c r="E50">
         <v>3</v>
       </c>
-      <c r="F47">
+      <c r="F50">
         <v>1</v>
       </c>
     </row>
@@ -2245,7 +2314,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -2584,7 +2653,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2130</v>
+        <v>2060</v>
       </c>
       <c r="B31" t="s">
         <v>62</v>
@@ -2595,178 +2664,211 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>3010</v>
-      </c>
-      <c r="B32" s="1" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B32" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>64</v>
+      <c r="C32" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
+        <v>2080</v>
+      </c>
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>2130</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>3010</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
         <v>3020</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" ht="39" spans="1:3">
-      <c r="A34">
-        <v>4010</v>
-      </c>
-      <c r="B34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" ht="39" spans="1:3">
-      <c r="A35">
-        <v>4020</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="C36" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" ht="39" spans="1:3">
-      <c r="A36">
-        <v>4030</v>
-      </c>
-      <c r="B36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="37" ht="39" spans="1:3">
       <c r="A37">
+        <v>4010</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" ht="39" spans="1:3">
+      <c r="A38">
+        <v>4020</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" ht="39" spans="1:3">
+      <c r="A39">
+        <v>4030</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" ht="39" spans="1:3">
+      <c r="A40">
         <v>4040</v>
       </c>
-      <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38">
-        <v>4110</v>
-      </c>
-      <c r="B38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B40" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39">
-        <v>4120</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="C40" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40">
-        <v>4130</v>
-      </c>
-      <c r="B40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>4140</v>
+        <v>4110</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>4150</v>
+        <v>4120</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>4210</v>
+        <v>4130</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>4220</v>
+        <v>4140</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>4230</v>
+        <v>4150</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>4240</v>
+        <v>4210</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
+        <v>4220</v>
+      </c>
+      <c r="B47" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>4230</v>
+      </c>
+      <c r="B48" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>4240</v>
+      </c>
+      <c r="B49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
         <v>4250</v>
       </c>
-      <c r="B47" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" t="s">
-        <v>94</v>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2888,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2794,10 +2896,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2805,10 +2907,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2816,10 +2918,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="108">
   <si>
     <t>Id</t>
   </si>
@@ -316,6 +316,12 @@
     <t>Spdを１アップ</t>
   </si>
   <si>
+    <t>マスタープルフ</t>
+  </si>
+  <si>
+    <t>クラスチェンジできる</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -335,6 +341,9 @@
   </si>
   <si>
     <t>Param1=Nu数</t>
+  </si>
+  <si>
+    <t>UseItem</t>
   </si>
 </sst>
 </file>
@@ -342,10 +351,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -365,29 +374,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -395,6 +382,20 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -408,30 +409,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,19 +425,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -473,6 +444,21 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -492,8 +478,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -501,7 +503,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -522,187 +531,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,21 +722,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -751,24 +745,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -799,6 +775,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -813,6 +798,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -821,145 +830,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1295,7 +1304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2303,6 +2312,26 @@
       </c>
       <c r="F50">
         <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>4310</v>
+      </c>
+      <c r="B51">
+        <v>226</v>
+      </c>
+      <c r="C51">
+        <v>40</v>
+      </c>
+      <c r="D51">
+        <v>40</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2314,7 +2343,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -2869,6 +2898,17 @@
       </c>
       <c r="C50" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>4310</v>
+      </c>
+      <c r="B51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2880,15 +2920,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2896,10 +2936,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2907,10 +2947,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2918,10 +2958,18 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -372,6 +372,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -387,36 +409,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -426,14 +418,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -448,14 +433,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -470,9 +455,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -485,36 +515,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -531,6 +531,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -543,175 +561,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,6 +722,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -742,9 +757,35 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -766,10 +807,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -783,45 +822,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -830,7 +830,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -839,7 +839,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -848,127 +848,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1958,7 +1958,7 @@
         <v>20</v>
       </c>
       <c r="D33">
-        <v>310070</v>
+        <v>310080</v>
       </c>
       <c r="E33">
         <v>0</v>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="115">
   <si>
     <t>Id</t>
   </si>
@@ -322,6 +322,24 @@
     <t>クラスチェンジできる</t>
   </si>
   <si>
+    <t>ダークボトル</t>
+  </si>
+  <si>
+    <t>一定ターンの間エンカウントしやすくなる</t>
+  </si>
+  <si>
+    <t>ホーリーボトル</t>
+  </si>
+  <si>
+    <t>一定ターンの間エンカウントしにくくなる</t>
+  </si>
+  <si>
+    <t>聖者の祈祷酒</t>
+  </si>
+  <si>
+    <t>一定ターンの間エンカウントしなくなる</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -344,6 +362,9 @@
   </si>
   <si>
     <t>UseItem</t>
+  </si>
+  <si>
+    <t>DungeonItem</t>
   </si>
 </sst>
 </file>
@@ -351,9 +372,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -373,45 +394,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -426,66 +409,20 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -501,10 +438,79 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -515,6 +521,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -531,7 +552,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,19 +606,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,31 +654,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -603,31 +702,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -639,79 +714,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,13 +776,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -769,8 +794,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -790,21 +815,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -817,8 +827,19 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -830,145 +851,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1304,7 +1325,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2333,6 +2354,69 @@
       <c r="F51">
         <v>0</v>
       </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>5010</v>
+      </c>
+      <c r="B52">
+        <v>125</v>
+      </c>
+      <c r="C52">
+        <v>50</v>
+      </c>
+      <c r="D52">
+        <v>50</v>
+      </c>
+      <c r="E52">
+        <v>150</v>
+      </c>
+      <c r="F52">
+        <v>25</v>
+      </c>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>5020</v>
+      </c>
+      <c r="B53">
+        <v>125</v>
+      </c>
+      <c r="C53">
+        <v>50</v>
+      </c>
+      <c r="D53">
+        <v>50</v>
+      </c>
+      <c r="E53">
+        <v>50</v>
+      </c>
+      <c r="F53">
+        <v>25</v>
+      </c>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>5030</v>
+      </c>
+      <c r="B54">
+        <v>125</v>
+      </c>
+      <c r="C54">
+        <v>50</v>
+      </c>
+      <c r="D54">
+        <v>50</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>25</v>
+      </c>
+      <c r="G54" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2343,7 +2427,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -2909,6 +2993,39 @@
       </c>
       <c r="C51" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>5010</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>5020</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>5030</v>
+      </c>
+      <c r="B54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C54" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2920,15 +3037,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2936,10 +3053,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2947,10 +3064,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2958,10 +3075,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2969,7 +3086,15 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="118">
   <si>
     <t>Id</t>
   </si>
@@ -232,28 +232,28 @@
   </si>
   <si>
     <t>Expを50入手する
-Lvが10以下の場合、取得経験値が2倍になる</t>
+Lvが10以下の場合は取得経験値が2倍になる</t>
   </si>
   <si>
     <t>中級指南書</t>
   </si>
   <si>
     <t>Expを50入手する
-Lvが20以下の場合、取得経験値が2倍になる</t>
+Lvが20以下の場合は取得経験値が2倍になる</t>
   </si>
   <si>
     <t>上級指南書</t>
   </si>
   <si>
     <t>Expを50入手する
-Lvが30以下の場合、取得経験値が2倍になる</t>
+Lvが30以下の場合は取得経験値が2倍になる</t>
   </si>
   <si>
     <t>特級指南書</t>
   </si>
   <si>
     <t>Expを50入手する
-Lvが40以下の場合、取得経験値が2倍になる</t>
+Lvが40以下の場合は取得経験値が2倍になる</t>
   </si>
   <si>
     <t>レッドスピネル</t>
@@ -340,6 +340,12 @@
     <t>一定ターンの間エンカウントしなくなる</t>
   </si>
   <si>
+    <t>隠遁のヴェール</t>
+  </si>
+  <si>
+    <t>ダンジョンにいられる猶予ターンを10増やす</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -365,6 +371,9 @@
   </si>
   <si>
     <t>DungeonItem</t>
+  </si>
+  <si>
+    <t>DungeonTurn</t>
   </si>
 </sst>
 </file>
@@ -401,7 +410,54 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -415,16 +471,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -440,30 +503,22 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -471,20 +526,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -498,38 +539,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -552,7 +561,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -564,19 +645,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -588,7 +657,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -600,13 +675,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -618,115 +729,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,6 +752,50 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -762,16 +815,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -799,50 +852,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -851,7 +860,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -860,7 +869,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -869,127 +878,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1325,7 +1334,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2417,6 +2426,27 @@
         <v>25</v>
       </c>
       <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>5040</v>
+      </c>
+      <c r="B55">
+        <v>125</v>
+      </c>
+      <c r="C55">
+        <v>60</v>
+      </c>
+      <c r="D55">
+        <v>10</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2427,7 +2457,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -3026,6 +3056,17 @@
       </c>
       <c r="C54" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>5040</v>
+      </c>
+      <c r="B55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3037,15 +3078,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3053,10 +3094,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3064,10 +3105,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3075,10 +3116,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3086,7 +3127,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3094,7 +3135,15 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -381,9 +381,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -402,10 +402,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -417,55 +418,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -480,22 +433,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -509,23 +447,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -540,7 +463,84 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -561,13 +561,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,61 +723,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -645,103 +741,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -770,6 +770,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -784,8 +823,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -813,45 +852,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -860,16 +860,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -878,127 +878,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2435,13 +2435,13 @@
         <v>125</v>
       </c>
       <c r="C55">
+        <v>50</v>
+      </c>
+      <c r="D55">
         <v>60</v>
       </c>
-      <c r="D55">
-        <v>10</v>
-      </c>
       <c r="E55">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F55">
         <v>0</v>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -42,112 +42,112 @@
     <t>Help</t>
   </si>
   <si>
-    <t>虹の原石</t>
-  </si>
-  <si>
-    <t>Rank.NのPassive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>炎の原石</t>
-  </si>
-  <si>
-    <t>Rank.Nの炎属性Passive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>雷の原石</t>
-  </si>
-  <si>
-    <t>Rank.Nの雷属性Passive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>氷の原石</t>
-  </si>
-  <si>
-    <t>Rank.Nの氷属性Passive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>光の原石</t>
-  </si>
-  <si>
-    <t>Rank.Nの光属性Passive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>闇の原石</t>
-  </si>
-  <si>
-    <t>Rank.Nの闇属性Passive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>虹の魔晶石</t>
-  </si>
-  <si>
-    <t>Rank.RのPassive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>炎の魔晶石</t>
-  </si>
-  <si>
-    <t>Rank.Rの炎属性Passive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>雷の魔晶石</t>
-  </si>
-  <si>
-    <t>Rank.Rの雷属性Passive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>氷の魔晶石</t>
-  </si>
-  <si>
-    <t>Rank.Rの氷属性Passive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>光の魔晶石</t>
-  </si>
-  <si>
-    <t>Rank.Rの光属性Passive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>闇の魔晶石</t>
-  </si>
-  <si>
-    <t>Rank.Rの闇属性Passive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>虹の指南書</t>
-  </si>
-  <si>
-    <t>Rank.RのActive魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>炎の指南書</t>
-  </si>
-  <si>
-    <t>Rank.Rの炎属性Active魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>雷の指南書</t>
-  </si>
-  <si>
-    <t>Rank.Rの雷属性Active魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>氷の指南書</t>
-  </si>
-  <si>
-    <t>Rank.Rの氷属性Active魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>光の指南書</t>
-  </si>
-  <si>
-    <t>Rank.Rの光属性Active魔法をランダムで入手</t>
-  </si>
-  <si>
-    <t>闇の指南書</t>
-  </si>
-  <si>
-    <t>Rank.Rの闇属性Active魔法をランダムで入手</t>
+    <t>虹の指南書(見習い)</t>
+  </si>
+  <si>
+    <t>Rank.Nの魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>炎の指南書(見習い)</t>
+  </si>
+  <si>
+    <t>Rank.Nの炎属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>雷の指南書(見習い)</t>
+  </si>
+  <si>
+    <t>Rank.Nの雷属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>氷の指南書(見習い)</t>
+  </si>
+  <si>
+    <t>Rank.Nの氷属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>光の指南書(見習い)</t>
+  </si>
+  <si>
+    <t>Rank.Nの光属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>闇の指南書(見習い)</t>
+  </si>
+  <si>
+    <t>Rank.Nの闇属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>虹の指南書(精通)</t>
+  </si>
+  <si>
+    <t>Rank.Rの魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>炎の指南書(精通)</t>
+  </si>
+  <si>
+    <t>Rank.Rの炎属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>雷の指南書(精通)</t>
+  </si>
+  <si>
+    <t>Rank.Rの雷属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>氷の指南書(精通)</t>
+  </si>
+  <si>
+    <t>Rank.Rの氷属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>光の指南書(精通)</t>
+  </si>
+  <si>
+    <t>Rank.Rの光属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>闇の指南書(精通)</t>
+  </si>
+  <si>
+    <t>Rank.Rの闇属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>虹の指南書(熟練者)</t>
+  </si>
+  <si>
+    <t>Rank.SRの魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>炎の指南書(熟練者)</t>
+  </si>
+  <si>
+    <t>Rank.SRの炎属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>雷の指南書(熟練者)</t>
+  </si>
+  <si>
+    <t>Rank.SRの雷属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>氷の指南書(熟練者)</t>
+  </si>
+  <si>
+    <t>Rank.SRの氷属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>光の指南書(熟練者)</t>
+  </si>
+  <si>
+    <t>Rank.SRの光属性魔法をランダムで入手</t>
+  </si>
+  <si>
+    <t>闇の指南書(熟練者)</t>
+  </si>
+  <si>
+    <t>Rank.SRの闇属性魔法をランダムで入手</t>
   </si>
   <si>
     <t>虹の精霊輝石</t>
@@ -382,9 +382,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -410,20 +410,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -433,7 +419,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -448,57 +434,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -522,6 +464,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -530,11 +479,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -545,6 +538,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -561,7 +561,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,175 +735,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,17 +755,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -788,8 +782,43 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -805,35 +834,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -860,145 +860,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1368,7 +1368,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>-1</v>
@@ -1388,7 +1388,7 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1408,7 +1408,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1428,7 +1428,7 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1448,7 +1448,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -1468,7 +1468,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>-1</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -1548,7 +1548,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -1568,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -1588,7 +1588,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -1608,7 +1608,7 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>-1</v>
@@ -1628,7 +1628,7 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -1668,7 +1668,7 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1688,7 +1688,7 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -1708,7 +1708,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -2460,7 +2460,7 @@
   <dimension ref="A1:C55"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
+    <col min="2" max="2" width="19.8181818181818" customWidth="1"/>
     <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
     <t>商売の才覚書</t>
   </si>
   <si>
-    <t xml:space="preserve">ワタリガラスの旗 </t>
+    <t>メビウスの砂時計</t>
   </si>
   <si>
     <t>先陣の心得</t>
@@ -381,9 +381,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -402,6 +402,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -410,31 +425,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -442,17 +434,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -465,7 +449,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -480,7 +471,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -501,14 +516,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -517,7 +524,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -530,21 +545,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -561,7 +561,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,7 +639,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,13 +693,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -603,109 +723,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -717,31 +741,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,6 +752,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -775,15 +790,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -812,17 +818,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -838,17 +833,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -860,145 +860,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="120">
   <si>
     <t>Id</t>
   </si>
@@ -344,6 +344,12 @@
   </si>
   <si>
     <t>ダンジョンにいられる猶予ターンを10増やす</t>
+  </si>
+  <si>
+    <t>ポーション</t>
+  </si>
+  <si>
+    <t>仲間全員のHpを10回復する</t>
   </si>
   <si>
     <t>Type</t>
@@ -381,9 +387,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -402,39 +408,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -448,25 +431,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -479,7 +462,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -493,16 +476,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -517,16 +500,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -539,10 +538,17 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -561,7 +567,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,19 +699,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -597,97 +717,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -699,49 +741,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,45 +758,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -852,6 +819,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -860,145 +866,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1334,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2447,6 +2453,27 @@
         <v>0</v>
       </c>
       <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>5050</v>
+      </c>
+      <c r="B56">
+        <v>125</v>
+      </c>
+      <c r="C56">
+        <v>50</v>
+      </c>
+      <c r="D56">
+        <v>70</v>
+      </c>
+      <c r="E56">
+        <v>10</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2457,7 +2484,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="19.8181818181818" customWidth="1"/>
@@ -3067,6 +3094,17 @@
       </c>
       <c r="C55" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>5050</v>
+      </c>
+      <c r="B56" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3086,7 +3124,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3094,10 +3132,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3105,10 +3143,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3116,10 +3154,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3127,7 +3165,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3135,7 +3173,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3143,7 +3181,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="122">
   <si>
     <t>Id</t>
   </si>
@@ -325,19 +325,22 @@
     <t>ダークボトル</t>
   </si>
   <si>
-    <t>一定ターンの間エンカウントしやすくなる</t>
+    <t>&lt;ダンジョン専用アイテム&gt;
+一定期間の間エンカウントしやすくなる</t>
   </si>
   <si>
     <t>ホーリーボトル</t>
   </si>
   <si>
-    <t>一定ターンの間エンカウントしにくくなる</t>
+    <t>&lt;ダンジョン専用アイテム&gt;
+一定期間の間エンカウントしにくくなる</t>
   </si>
   <si>
     <t>聖者の祈祷酒</t>
   </si>
   <si>
-    <t>一定ターンの間エンカウントしなくなる</t>
+    <t>&lt;ダンジョン専用アイテム&gt;
+一定期間の間エンカウントしなくなる</t>
   </si>
   <si>
     <t>隠遁のヴェール</t>
@@ -349,7 +352,15 @@
     <t>ポーション</t>
   </si>
   <si>
-    <t>仲間全員のHpを10回復する</t>
+    <t>&lt;ダンジョン専用アイテム&gt;
+仲間全員のHpを10回復する</t>
+  </si>
+  <si>
+    <t>ハイポーション</t>
+  </si>
+  <si>
+    <t>&lt;ダンジョン専用アイテム&gt;
+仲間全員のHpを20回復する</t>
   </si>
   <si>
     <t>Type</t>
@@ -408,9 +419,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -423,46 +442,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -477,7 +458,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -485,13 +466,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -499,37 +479,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -546,7 +495,69 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -573,7 +584,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,7 +626,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -597,7 +662,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -615,7 +692,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -627,61 +734,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,61 +752,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -785,17 +796,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -814,8 +834,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -834,30 +869,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -866,7 +877,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -875,7 +886,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -884,136 +895,139 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1340,7 +1354,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1724,122 +1738,122 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>1300</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>11</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="4">
         <v>11</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="4">
         <v>110</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="4">
         <v>-1</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="3">
+      <c r="A21" s="4">
         <v>1310</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>11</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <v>11</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>110</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="3">
+      <c r="A22" s="4">
         <v>1320</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>11</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="4">
         <v>11</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="4">
         <v>110</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="4">
         <v>2</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="3">
+      <c r="A23" s="4">
         <v>1330</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>11</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="4">
         <v>11</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="4">
         <v>110</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="4">
         <v>3</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="3">
+      <c r="A24" s="4">
         <v>1340</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>11</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="4">
         <v>11</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="4">
         <v>110</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="4">
         <v>4</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="3">
+      <c r="A25" s="4">
         <v>1350</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>11</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="4">
         <v>11</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="4">
         <v>110</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="4">
         <v>5</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2474,6 +2488,26 @@
         <v>0</v>
       </c>
       <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>5060</v>
+      </c>
+      <c r="B57">
+        <v>125</v>
+      </c>
+      <c r="C57">
+        <v>50</v>
+      </c>
+      <c r="D57">
+        <v>70</v>
+      </c>
+      <c r="E57">
+        <v>20</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2484,7 +2518,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="19.8181818181818" customWidth="1"/>
@@ -3052,36 +3086,36 @@
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" ht="39" spans="1:3">
       <c r="A52">
         <v>5010</v>
       </c>
       <c r="B52" t="s">
         <v>100</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" ht="39" spans="1:3">
       <c r="A53">
         <v>5020</v>
       </c>
       <c r="B53" t="s">
         <v>102</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" ht="39" spans="1:3">
       <c r="A54">
         <v>5030</v>
       </c>
       <c r="B54" t="s">
         <v>104</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="3" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3096,15 +3130,26 @@
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" ht="26" spans="1:3">
       <c r="A56">
         <v>5050</v>
       </c>
       <c r="B56" t="s">
         <v>108</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="3" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="57" ht="26" spans="1:3">
+      <c r="A57">
+        <v>5060</v>
+      </c>
+      <c r="B57" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3124,7 +3169,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3132,10 +3177,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3143,10 +3188,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3154,10 +3199,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3165,7 +3210,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3173,7 +3218,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3181,7 +3226,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -399,9 +399,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -419,41 +419,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -473,44 +449,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -532,16 +486,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -556,12 +509,59 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -578,7 +578,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,7 +662,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,145 +746,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,13 +758,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,6 +769,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -790,8 +814,34 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -799,8 +849,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -819,56 +869,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -877,7 +877,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -886,148 +886,145 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1044,12 +1041,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1738,122 +1735,122 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>1300</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>11</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="3">
         <v>11</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>110</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <v>-1</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>1310</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>11</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>11</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>110</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>1</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>1320</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>11</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="3">
         <v>11</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>110</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <v>2</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>1330</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="3">
         <v>11</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="3">
         <v>11</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>110</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="3">
         <v>3</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>1340</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="3">
         <v>11</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3">
         <v>11</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>110</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="3">
         <v>4</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>1350</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>11</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>11</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>110</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="3">
         <v>5</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="3">
         <v>0</v>
       </c>
     </row>
@@ -3093,7 +3090,7 @@
       <c r="B52" t="s">
         <v>100</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3104,7 +3101,7 @@
       <c r="B53" t="s">
         <v>102</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3115,7 +3112,7 @@
       <c r="B54" t="s">
         <v>104</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3137,7 +3134,7 @@
       <c r="B56" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3148,7 +3145,7 @@
       <c r="B57" t="s">
         <v>110</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>111</v>
       </c>
     </row>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="123">
   <si>
     <t>Id</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>Param3</t>
+  </si>
+  <si>
+    <t>Cost</t>
   </si>
   <si>
     <t>Text</t>
@@ -398,9 +401,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -420,14 +423,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -435,6 +431,22 @@
     <font>
       <b/>
       <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -455,16 +467,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -478,7 +491,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -493,50 +543,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -550,14 +561,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -578,7 +581,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,19 +593,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,7 +635,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,7 +689,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,73 +725,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,31 +749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,7 +761,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,6 +772,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -783,15 +795,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -813,6 +816,26 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -820,13 +843,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -845,30 +872,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -877,145 +880,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1354,7 +1357,7 @@
   <dimension ref="A1:G57"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1373,8 +1376,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -1393,8 +1399,11 @@
       <c r="F2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1010</v>
       </c>
@@ -1413,8 +1422,11 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -1433,8 +1445,11 @@
       <c r="F4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -1453,8 +1468,11 @@
       <c r="F5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -1473,8 +1491,11 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1050</v>
       </c>
@@ -1493,8 +1514,11 @@
       <c r="F7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1100</v>
       </c>
@@ -1513,8 +1537,11 @@
       <c r="F8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>1110</v>
       </c>
@@ -1533,8 +1560,11 @@
       <c r="F9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>1120</v>
       </c>
@@ -1553,8 +1583,11 @@
       <c r="F10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>1130</v>
       </c>
@@ -1573,8 +1606,11 @@
       <c r="F11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>1140</v>
       </c>
@@ -1593,8 +1629,11 @@
       <c r="F12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>1150</v>
       </c>
@@ -1613,8 +1652,11 @@
       <c r="F13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>1200</v>
       </c>
@@ -1633,8 +1675,11 @@
       <c r="F14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>1210</v>
       </c>
@@ -1653,8 +1698,11 @@
       <c r="F15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>1220</v>
       </c>
@@ -1673,8 +1721,11 @@
       <c r="F16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>1230</v>
       </c>
@@ -1693,8 +1744,11 @@
       <c r="F17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>1240</v>
       </c>
@@ -1713,8 +1767,11 @@
       <c r="F18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>1250</v>
       </c>
@@ -1733,8 +1790,11 @@
       <c r="F19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="3">
         <v>1300</v>
       </c>
@@ -1753,8 +1813,11 @@
       <c r="F20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="3">
         <v>1310</v>
       </c>
@@ -1773,8 +1836,11 @@
       <c r="F21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="3">
         <v>1320</v>
       </c>
@@ -1793,8 +1859,11 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="3">
         <v>1330</v>
       </c>
@@ -1813,8 +1882,11 @@
       <c r="F23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="3">
         <v>1340</v>
       </c>
@@ -1833,8 +1905,11 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="3">
         <v>1350</v>
       </c>
@@ -1853,8 +1928,11 @@
       <c r="F25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>2010</v>
       </c>
@@ -1873,8 +1951,11 @@
       <c r="F26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>2020</v>
       </c>
@@ -1893,8 +1974,11 @@
       <c r="F27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>2030</v>
       </c>
@@ -1913,8 +1997,11 @@
       <c r="F28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>2040</v>
       </c>
@@ -1933,8 +2020,11 @@
       <c r="F29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>2050</v>
       </c>
@@ -1953,8 +2043,11 @@
       <c r="F30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>2060</v>
       </c>
@@ -1973,8 +2066,11 @@
       <c r="F31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>2070</v>
       </c>
@@ -1993,8 +2089,11 @@
       <c r="F32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>2080</v>
       </c>
@@ -2013,8 +2112,11 @@
       <c r="F33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>2130</v>
       </c>
@@ -2033,8 +2135,11 @@
       <c r="F34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3010</v>
       </c>
@@ -2053,8 +2158,11 @@
       <c r="F35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3020</v>
       </c>
@@ -2071,6 +2179,9 @@
         <v>0</v>
       </c>
       <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
         <v>0</v>
       </c>
     </row>
@@ -2093,7 +2204,9 @@
       <c r="F37">
         <v>10</v>
       </c>
-      <c r="G37" s="1"/>
+      <c r="G37" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
@@ -2114,7 +2227,9 @@
       <c r="F38">
         <v>20</v>
       </c>
-      <c r="G38" s="1"/>
+      <c r="G38" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
@@ -2135,7 +2250,9 @@
       <c r="F39">
         <v>30</v>
       </c>
-      <c r="G39" s="1"/>
+      <c r="G39" s="1">
+        <v>30</v>
+      </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
@@ -2156,7 +2273,9 @@
       <c r="F40">
         <v>40</v>
       </c>
-      <c r="G40" s="1"/>
+      <c r="G40" s="1">
+        <v>40</v>
+      </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
@@ -2177,7 +2296,9 @@
       <c r="F41">
         <v>1</v>
       </c>
-      <c r="G41" s="1"/>
+      <c r="G41" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
@@ -2198,7 +2319,9 @@
       <c r="F42">
         <v>1</v>
       </c>
-      <c r="G42" s="1"/>
+      <c r="G42" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
@@ -2219,9 +2342,11 @@
       <c r="F43">
         <v>1</v>
       </c>
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="G43" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4140</v>
       </c>
@@ -2240,8 +2365,11 @@
       <c r="F44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4150</v>
       </c>
@@ -2260,8 +2388,11 @@
       <c r="F45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="G45" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4210</v>
       </c>
@@ -2280,8 +2411,11 @@
       <c r="F46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="G46" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4220</v>
       </c>
@@ -2300,8 +2434,11 @@
       <c r="F47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="G47" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>4230</v>
       </c>
@@ -2320,8 +2457,11 @@
       <c r="F48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>4240</v>
       </c>
@@ -2340,8 +2480,11 @@
       <c r="F49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="G49" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>4250</v>
       </c>
@@ -2360,8 +2503,11 @@
       <c r="F50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="G50" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>4310</v>
       </c>
@@ -2379,6 +2525,9 @@
       </c>
       <c r="F51">
         <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2400,7 +2549,9 @@
       <c r="F52">
         <v>25</v>
       </c>
-      <c r="G52" s="1"/>
+      <c r="G52" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
@@ -2421,7 +2572,9 @@
       <c r="F53">
         <v>25</v>
       </c>
-      <c r="G53" s="1"/>
+      <c r="G53" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
@@ -2442,7 +2595,9 @@
       <c r="F54">
         <v>25</v>
       </c>
-      <c r="G54" s="1"/>
+      <c r="G54" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
@@ -2463,7 +2618,9 @@
       <c r="F55">
         <v>0</v>
       </c>
-      <c r="G55" s="1"/>
+      <c r="G55" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
@@ -2484,9 +2641,11 @@
       <c r="F56">
         <v>0</v>
       </c>
-      <c r="G56" s="1"/>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>5060</v>
       </c>
@@ -2504,6 +2663,9 @@
       </c>
       <c r="F57">
         <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2527,10 +2689,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2538,10 +2700,10 @@
         <v>1000</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2549,10 +2711,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2560,10 +2722,10 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2571,10 +2733,10 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2582,10 +2744,10 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2593,10 +2755,10 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2604,10 +2766,10 @@
         <v>1100</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2615,10 +2777,10 @@
         <v>1110</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2626,10 +2788,10 @@
         <v>1120</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2637,10 +2799,10 @@
         <v>1130</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2648,10 +2810,10 @@
         <v>1140</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2659,10 +2821,10 @@
         <v>1150</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2670,10 +2832,10 @@
         <v>1200</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2681,10 +2843,10 @@
         <v>1210</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2692,10 +2854,10 @@
         <v>1220</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2703,10 +2865,10 @@
         <v>1230</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2714,10 +2876,10 @@
         <v>1240</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2725,10 +2887,10 @@
         <v>1250</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2736,10 +2898,10 @@
         <v>1300</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2747,10 +2909,10 @@
         <v>1310</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2758,10 +2920,10 @@
         <v>1320</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2769,10 +2931,10 @@
         <v>1330</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2780,10 +2942,10 @@
         <v>1340</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2791,10 +2953,10 @@
         <v>1350</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2802,10 +2964,10 @@
         <v>2010</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2813,10 +2975,10 @@
         <v>2020</v>
       </c>
       <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
         <v>58</v>
-      </c>
-      <c r="C27" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2824,10 +2986,10 @@
         <v>2030</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2835,10 +2997,10 @@
         <v>2040</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2846,10 +3008,10 @@
         <v>2050</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2857,10 +3019,10 @@
         <v>2060</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2868,10 +3030,10 @@
         <v>2070</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2879,10 +3041,10 @@
         <v>2080</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2890,10 +3052,10 @@
         <v>2130</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2901,10 +3063,10 @@
         <v>3010</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2912,10 +3074,10 @@
         <v>3020</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" ht="39" spans="1:3">
@@ -2923,10 +3085,10 @@
         <v>4010</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" ht="39" spans="1:3">
@@ -2934,10 +3096,10 @@
         <v>4020</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" ht="39" spans="1:3">
@@ -2945,10 +3107,10 @@
         <v>4030</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" ht="39" spans="1:3">
@@ -2956,10 +3118,10 @@
         <v>4040</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2967,10 +3129,10 @@
         <v>4110</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2978,10 +3140,10 @@
         <v>4120</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2989,10 +3151,10 @@
         <v>4130</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -3000,10 +3162,10 @@
         <v>4140</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -3011,10 +3173,10 @@
         <v>4150</v>
       </c>
       <c r="B45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -3022,10 +3184,10 @@
         <v>4210</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -3033,10 +3195,10 @@
         <v>4220</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -3044,10 +3206,10 @@
         <v>4230</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -3055,10 +3217,10 @@
         <v>4240</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -3066,10 +3228,10 @@
         <v>4250</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -3077,10 +3239,10 @@
         <v>4310</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" ht="39" spans="1:3">
@@ -3088,10 +3250,10 @@
         <v>5010</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" ht="39" spans="1:3">
@@ -3099,10 +3261,10 @@
         <v>5020</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" ht="39" spans="1:3">
@@ -3110,10 +3272,10 @@
         <v>5030</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -3121,10 +3283,10 @@
         <v>5040</v>
       </c>
       <c r="B55" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C55" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" ht="26" spans="1:3">
@@ -3132,10 +3294,10 @@
         <v>5050</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" ht="26" spans="1:3">
@@ -3143,10 +3305,10 @@
         <v>5060</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3328,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3174,10 +3336,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3185,10 +3347,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3196,10 +3358,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3207,7 +3369,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3215,7 +3377,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3223,7 +3385,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
     <t>妖精の祈り</t>
   </si>
   <si>
-    <t>信仰度+5</t>
+    <t>評価値+10</t>
   </si>
   <si>
     <t>月のかけら</t>
@@ -401,10 +401,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -422,51 +422,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -475,17 +430,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -505,19 +451,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -530,22 +467,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -561,6 +483,84 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -581,7 +581,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,19 +605,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,13 +665,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,13 +677,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,7 +695,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -671,31 +719,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,19 +731,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,25 +749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -761,7 +761,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -775,11 +775,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -800,16 +806,34 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -821,24 +845,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -858,17 +864,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -880,145 +880,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -222,13 +222,13 @@
     <t>金塊</t>
   </si>
   <si>
-    <t>10(Nu)に換金できる</t>
+    <t>50(Nu)に換金できる</t>
   </si>
   <si>
     <t>ダイアモンド</t>
   </si>
   <si>
-    <t>20(Nu)に換金できる</t>
+    <t>200(Nu)に換金できる</t>
   </si>
   <si>
     <t>初級指南書</t>
@@ -422,21 +422,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -452,37 +437,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -503,11 +458,73 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -526,19 +543,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -550,17 +559,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -581,7 +581,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,13 +635,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,7 +659,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -623,133 +743,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -761,7 +755,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -805,21 +805,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -832,19 +817,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -864,11 +838,37 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -880,7 +880,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -889,136 +889,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2150,7 +2150,7 @@
         <v>30</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>30</v>
       </c>
       <c r="D36">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2205,7 +2205,7 @@
         <v>10</v>
       </c>
       <c r="G37" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2228,7 +2228,7 @@
         <v>20</v>
       </c>
       <c r="G38" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2251,7 +2251,7 @@
         <v>30</v>
       </c>
       <c r="G39" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2274,7 +2274,7 @@
         <v>40</v>
       </c>
       <c r="G40" s="1">
-        <v>40</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2297,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2320,7 +2320,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2343,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2366,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2389,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2412,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2435,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2458,7 +2458,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2481,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2504,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2527,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -356,14 +356,14 @@
   </si>
   <si>
     <t>&lt;ダンジョン専用アイテム&gt;
-仲間全員のHpを10回復する</t>
+仲間全員のHpを20回復する</t>
   </si>
   <si>
     <t>ハイポーション</t>
   </si>
   <si>
     <t>&lt;ダンジョン専用アイテム&gt;
-仲間全員のHpを20回復する</t>
+仲間全員のHpを50回復する</t>
   </si>
   <si>
     <t>Type</t>
@@ -403,8 +403,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -423,14 +423,52 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -443,8 +481,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -459,23 +521,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -491,14 +537,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -512,55 +551,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -581,7 +581,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,115 +599,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,7 +623,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,37 +737,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,21 +776,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -801,39 +786,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -855,10 +807,32 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -872,6 +846,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -880,145 +880,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2636,7 +2636,7 @@
         <v>70</v>
       </c>
       <c r="E56">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2659,7 +2659,7 @@
         <v>70</v>
       </c>
       <c r="E57">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F57">
         <v>0</v>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -51,10 +51,10 @@
     <t>Rank.Nの魔法をランダムで入手</t>
   </si>
   <si>
-    <t>炎の指南書(見習い)</t>
-  </si>
-  <si>
-    <t>Rank.Nの炎属性魔法をランダムで入手</t>
+    <t>炎の紋章召喚(初級)</t>
+  </si>
+  <si>
+    <t>Rank.Nの炎属性紋章をランダムで入手</t>
   </si>
   <si>
     <t>雷の指南書(見習い)</t>
@@ -401,9 +401,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -423,14 +423,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -443,39 +451,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -497,16 +474,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -521,7 +498,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -545,14 +552,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -560,7 +560,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -581,19 +581,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,13 +641,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -623,25 +665,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,97 +677,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -761,7 +695,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -786,30 +786,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -847,13 +823,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -872,6 +861,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -880,7 +880,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -889,136 +889,136 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -45,7 +45,7 @@
     <t>Help</t>
   </si>
   <si>
-    <t>虹の指南書(見習い)</t>
+    <t>虹の紋章召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの魔法をランダムで入手</t>
@@ -57,25 +57,25 @@
     <t>Rank.Nの炎属性紋章をランダムで入手</t>
   </si>
   <si>
-    <t>雷の指南書(見習い)</t>
+    <t>雷の紋章召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの雷属性魔法をランダムで入手</t>
   </si>
   <si>
-    <t>氷の指南書(見習い)</t>
+    <t>氷の紋章召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの氷属性魔法をランダムで入手</t>
   </si>
   <si>
-    <t>光の指南書(見習い)</t>
+    <t>光の紋章召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの光属性魔法をランダムで入手</t>
   </si>
   <si>
-    <t>闇の指南書(見習い)</t>
+    <t>闇の紋章召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの闇属性魔法をランダムで入手</t>
@@ -401,10 +401,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -422,13 +422,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -438,9 +431,78 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -459,7 +521,23 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -481,86 +559,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -587,7 +587,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,13 +683,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -623,37 +743,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,103 +761,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -790,17 +790,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -824,40 +839,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -872,6 +863,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -880,145 +880,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -422,6 +422,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -431,7 +468,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,17 +489,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -463,21 +499,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -499,6 +520,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -506,15 +535,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -528,39 +551,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -581,7 +581,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,19 +659,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,13 +707,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,19 +719,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,85 +761,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,6 +772,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -790,6 +799,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -801,6 +819,30 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -822,39 +864,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -863,15 +872,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -880,7 +880,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -889,136 +889,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
     <t>虹の紋章召喚(初級)</t>
   </si>
   <si>
-    <t>Rank.Nの魔法をランダムで入手</t>
+    <t>Rank.Nの魔法を1つ選んで入手</t>
   </si>
   <si>
     <t>炎の紋章召喚(初級)</t>
@@ -402,8 +402,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -429,31 +429,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -475,7 +452,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -483,29 +475,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -520,14 +498,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -535,9 +505,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -551,16 +550,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -581,13 +581,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,13 +599,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -623,7 +737,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,133 +755,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,15 +772,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -799,30 +790,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -834,15 +801,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -864,6 +822,33 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -872,6 +857,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -880,145 +880,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1388,7 +1388,7 @@
         <v>137</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -48,109 +48,109 @@
     <t>虹の紋章召喚(初級)</t>
   </si>
   <si>
-    <t>Rank.Nの魔法を1つ選んで入手</t>
+    <t>Rank.Nの装具を選んで入手</t>
   </si>
   <si>
     <t>炎の紋章召喚(初級)</t>
   </si>
   <si>
-    <t>Rank.Nの炎属性紋章をランダムで入手</t>
+    <t>Rank.Nの炎属性装具を選んで入手</t>
   </si>
   <si>
     <t>雷の紋章召喚(初級)</t>
   </si>
   <si>
-    <t>Rank.Nの雷属性魔法をランダムで入手</t>
+    <t>Rank.Nの雷属性装具を選んで入手</t>
   </si>
   <si>
     <t>氷の紋章召喚(初級)</t>
   </si>
   <si>
-    <t>Rank.Nの氷属性魔法をランダムで入手</t>
+    <t>Rank.Nの氷属性装具を選んで入手</t>
   </si>
   <si>
     <t>光の紋章召喚(初級)</t>
   </si>
   <si>
-    <t>Rank.Nの光属性魔法をランダムで入手</t>
+    <t>Rank.Nの光属性装具を選んで入手</t>
   </si>
   <si>
     <t>闇の紋章召喚(初級)</t>
   </si>
   <si>
-    <t>Rank.Nの闇属性魔法をランダムで入手</t>
+    <t>Rank.Nの闇属性装具を選んで入手</t>
   </si>
   <si>
     <t>虹の指南書(精通)</t>
   </si>
   <si>
-    <t>Rank.Rの魔法をランダムで入手</t>
+    <t>Rank.Rの装具を選んで入手</t>
   </si>
   <si>
     <t>炎の指南書(精通)</t>
   </si>
   <si>
-    <t>Rank.Rの炎属性魔法をランダムで入手</t>
+    <t>Rank.Rの炎属性装具を選んで入手</t>
   </si>
   <si>
     <t>雷の指南書(精通)</t>
   </si>
   <si>
-    <t>Rank.Rの雷属性魔法をランダムで入手</t>
+    <t>Rank.Rの雷属性装具を選んで入手</t>
   </si>
   <si>
     <t>氷の指南書(精通)</t>
   </si>
   <si>
-    <t>Rank.Rの氷属性魔法をランダムで入手</t>
+    <t>Rank.Rの氷属性装具を選んで入手</t>
   </si>
   <si>
     <t>光の指南書(精通)</t>
   </si>
   <si>
-    <t>Rank.Rの光属性魔法をランダムで入手</t>
+    <t>Rank.Rの光属性装具を選んで入手</t>
   </si>
   <si>
     <t>闇の指南書(精通)</t>
   </si>
   <si>
-    <t>Rank.Rの闇属性魔法をランダムで入手</t>
+    <t>Rank.Rの闇属性装具を選んで入手</t>
   </si>
   <si>
     <t>虹の指南書(熟練者)</t>
   </si>
   <si>
-    <t>Rank.SRの魔法をランダムで入手</t>
+    <t>Rank.SRの装具を選んで入手</t>
   </si>
   <si>
     <t>炎の指南書(熟練者)</t>
   </si>
   <si>
-    <t>Rank.SRの炎属性魔法をランダムで入手</t>
+    <t>Rank.SRの炎属性装具を選んで入手</t>
   </si>
   <si>
     <t>雷の指南書(熟練者)</t>
   </si>
   <si>
-    <t>Rank.SRの雷属性魔法をランダムで入手</t>
+    <t>Rank.SRの雷属性装具を選んで入手</t>
   </si>
   <si>
     <t>氷の指南書(熟練者)</t>
   </si>
   <si>
-    <t>Rank.SRの氷属性魔法をランダムで入手</t>
+    <t>Rank.SRの氷属性装具を選んで入手</t>
   </si>
   <si>
     <t>光の指南書(熟練者)</t>
   </si>
   <si>
-    <t>Rank.SRの光属性魔法をランダムで入手</t>
+    <t>Rank.SRの光属性装具を選んで入手</t>
   </si>
   <si>
     <t>闇の指南書(熟練者)</t>
   </si>
   <si>
-    <t>Rank.SRの闇属性魔法をランダムで入手</t>
+    <t>Rank.SRの闇属性装具を選んで入手</t>
   </si>
   <si>
     <t>虹の精霊輝石</t>
@@ -401,10 +401,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -423,28 +423,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -452,38 +430,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -498,21 +445,13 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -529,14 +468,76 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -551,16 +552,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -581,25 +581,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,19 +599,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -647,25 +701,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -677,43 +719,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,37 +743,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,6 +772,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -805,55 +823,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -872,6 +846,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -880,7 +880,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -889,136 +889,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1411,7 +1411,7 @@
         <v>137</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1434,7 +1434,7 @@
         <v>137</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1457,7 +1457,7 @@
         <v>137</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1480,7 +1480,7 @@
         <v>137</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1503,7 +1503,7 @@
         <v>137</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1526,7 +1526,7 @@
         <v>137</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1549,7 +1549,7 @@
         <v>137</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1572,7 +1572,7 @@
         <v>137</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -1595,7 +1595,7 @@
         <v>137</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1618,7 +1618,7 @@
         <v>137</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1641,7 +1641,7 @@
         <v>137</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1664,7 +1664,7 @@
         <v>137</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -1687,7 +1687,7 @@
         <v>137</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -1710,7 +1710,7 @@
         <v>137</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -1733,7 +1733,7 @@
         <v>137</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1756,7 +1756,7 @@
         <v>137</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1779,7 +1779,7 @@
         <v>137</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19">
         <v>3</v>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -45,37 +45,37 @@
     <t>Help</t>
   </si>
   <si>
-    <t>虹の紋章召喚(初級)</t>
+    <t>虹の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの装具を選んで入手</t>
   </si>
   <si>
-    <t>炎の紋章召喚(初級)</t>
+    <t>炎の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの炎属性装具を選んで入手</t>
   </si>
   <si>
-    <t>雷の紋章召喚(初級)</t>
+    <t>雷の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの雷属性装具を選んで入手</t>
   </si>
   <si>
-    <t>氷の紋章召喚(初級)</t>
+    <t>氷の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの氷属性装具を選んで入手</t>
   </si>
   <si>
-    <t>光の紋章召喚(初級)</t>
+    <t>光の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの光属性装具を選んで入手</t>
   </si>
   <si>
-    <t>闇の紋章召喚(初級)</t>
+    <t>闇の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの闇属性装具を選んで入手</t>
@@ -422,45 +422,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -475,53 +438,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -537,7 +461,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -551,6 +482,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -559,8 +513,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -581,7 +581,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,13 +611,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,19 +683,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,37 +719,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -677,91 +755,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -784,15 +784,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -804,6 +795,41 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -826,23 +852,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -861,17 +872,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -880,7 +880,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -889,16 +889,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -907,118 +907,118 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="125">
   <si>
     <t>Id</t>
   </si>
@@ -43,6 +43,12 @@
   </si>
   <si>
     <t>Help</t>
+  </si>
+  <si>
+    <t>EnglishText</t>
+  </si>
+  <si>
+    <t>EnglishHelp</t>
   </si>
   <si>
     <t>虹の装具召喚(初級)</t>
@@ -401,10 +407,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -423,15 +429,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -439,6 +438,20 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -459,47 +472,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,6 +483,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -523,7 +505,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -537,7 +526,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -551,10 +540,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -563,6 +561,14 @@
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -581,13 +587,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,49 +641,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,19 +677,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,7 +689,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,67 +761,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,9 +783,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -814,26 +831,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -852,8 +849,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -872,6 +869,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -880,25 +886,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -907,118 +913,118 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2677,14 +2683,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C57"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="19.8181818181818" customWidth="1"/>
     <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="17.1909090909091" customWidth="1"/>
+    <col min="7" max="7" width="40.1636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2694,621 +2702,963 @@
       <c r="C1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1000</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1100</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>1110</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>1120</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>28</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>1130</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>1140</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>1150</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>34</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>1200</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>36</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>1210</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>38</v>
+      </c>
+      <c r="F15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>1220</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>1230</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>42</v>
+      </c>
+      <c r="F17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>1240</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>44</v>
+      </c>
+      <c r="F18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>1250</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>46</v>
+      </c>
+      <c r="F19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>1300</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>1310</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>1320</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>52</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>1330</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>54</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>1340</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="F24" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>1350</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>58</v>
+      </c>
+      <c r="F25" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>2010</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>60</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>2020</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>60</v>
+      </c>
+      <c r="F27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>2030</v>
       </c>
       <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
         <v>60</v>
       </c>
-      <c r="C28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="F28" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>2040</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>60</v>
+      </c>
+      <c r="F29" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>2050</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>60</v>
+      </c>
+      <c r="F30" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>2060</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>60</v>
+      </c>
+      <c r="F31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>2070</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>60</v>
+      </c>
+      <c r="F32" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>2080</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>60</v>
+      </c>
+      <c r="F33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>2130</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>60</v>
+      </c>
+      <c r="F34" t="s">
+        <v>68</v>
+      </c>
+      <c r="G34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3010</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>70</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3020</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" ht="39" spans="1:3">
+        <v>72</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" ht="39" spans="1:7">
       <c r="A37">
         <v>4010</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" ht="39" spans="1:3">
+        <v>74</v>
+      </c>
+      <c r="F37" t="s">
+        <v>73</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" ht="39" spans="1:7">
       <c r="A38">
         <v>4020</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" ht="39" spans="1:3">
+        <v>76</v>
+      </c>
+      <c r="F38" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" ht="39" spans="1:7">
       <c r="A39">
         <v>4030</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" ht="39" spans="1:3">
+        <v>78</v>
+      </c>
+      <c r="F39" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" ht="39" spans="1:7">
       <c r="A40">
         <v>4040</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>80</v>
+      </c>
+      <c r="F40" t="s">
+        <v>79</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4110</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>82</v>
+      </c>
+      <c r="F41" t="s">
+        <v>81</v>
+      </c>
+      <c r="G41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4120</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>84</v>
+      </c>
+      <c r="F42" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4130</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>86</v>
+      </c>
+      <c r="F43" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4140</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>88</v>
+      </c>
+      <c r="F44" t="s">
+        <v>87</v>
+      </c>
+      <c r="G44" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4150</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>90</v>
+      </c>
+      <c r="F45" t="s">
+        <v>89</v>
+      </c>
+      <c r="G45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4210</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>92</v>
+      </c>
+      <c r="F46" t="s">
+        <v>91</v>
+      </c>
+      <c r="G46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4220</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>94</v>
+      </c>
+      <c r="F47" t="s">
+        <v>93</v>
+      </c>
+      <c r="G47" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>4230</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>96</v>
+      </c>
+      <c r="F48" t="s">
+        <v>95</v>
+      </c>
+      <c r="G48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>4240</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>98</v>
+      </c>
+      <c r="F49" t="s">
+        <v>97</v>
+      </c>
+      <c r="G49" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>4250</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>100</v>
+      </c>
+      <c r="F50" t="s">
+        <v>99</v>
+      </c>
+      <c r="G50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>4310</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" ht="39" spans="1:3">
+        <v>102</v>
+      </c>
+      <c r="F51" t="s">
+        <v>101</v>
+      </c>
+      <c r="G51" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" ht="39" spans="1:7">
       <c r="A52">
         <v>5010</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" ht="39" spans="1:3">
+        <v>104</v>
+      </c>
+      <c r="F52" t="s">
+        <v>103</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" ht="39" spans="1:7">
       <c r="A53">
         <v>5020</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" ht="39" spans="1:3">
+        <v>106</v>
+      </c>
+      <c r="F53" t="s">
+        <v>105</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" ht="39" spans="1:7">
       <c r="A54">
         <v>5030</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>108</v>
+      </c>
+      <c r="F54" t="s">
+        <v>107</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>5040</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="56" ht="26" spans="1:3">
+        <v>110</v>
+      </c>
+      <c r="F55" t="s">
+        <v>109</v>
+      </c>
+      <c r="G55" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" ht="26" spans="1:7">
       <c r="A56">
         <v>5050</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="57" ht="26" spans="1:3">
+        <v>112</v>
+      </c>
+      <c r="F56" t="s">
+        <v>111</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" ht="26" spans="1:7">
       <c r="A57">
         <v>5060</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="F57" t="s">
+        <v>113</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3328,7 +3678,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3336,10 +3686,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3347,10 +3697,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3358,10 +3708,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3369,7 +3719,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3377,7 +3727,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3385,7 +3735,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="223">
   <si>
     <t>Id</t>
   </si>
@@ -57,184 +57,352 @@
     <t>Rank.Nの装具を選んで入手</t>
   </si>
   <si>
+    <t>Rainbow Gear Summon (Beginner)</t>
+  </si>
+  <si>
+    <t>Obtain Rank N Gear</t>
+  </si>
+  <si>
     <t>炎の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの炎属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Fire Gear Summon (Beginner)</t>
+  </si>
+  <si>
+    <t>Obtain Rank N Fire Gear</t>
+  </si>
+  <si>
     <t>雷の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの雷属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Thunder Gear Summon (Beginner)</t>
+  </si>
+  <si>
+    <t>Obtain Rank N Thunder Gear</t>
+  </si>
+  <si>
     <t>氷の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの氷属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Ice Gear Summon (Beginner)</t>
+  </si>
+  <si>
+    <t>Obtain Rank N Ice Gear</t>
+  </si>
+  <si>
     <t>光の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの光属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Light Gear Summon (Beginner)</t>
+  </si>
+  <si>
+    <t>Obtain Rank N Light Gear</t>
+  </si>
+  <si>
     <t>闇の装具召喚(初級)</t>
   </si>
   <si>
     <t>Rank.Nの闇属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Dark Gear Summon (Beginner)</t>
+  </si>
+  <si>
+    <t>Obtain Rank N Dark Gear</t>
+  </si>
+  <si>
     <t>虹の指南書(精通)</t>
   </si>
   <si>
     <t>Rank.Rの装具を選んで入手</t>
   </si>
   <si>
+    <t>Rainbow Guidebook (Expertise)</t>
+  </si>
+  <si>
+    <t>Obtain Rank R Gear</t>
+  </si>
+  <si>
     <t>炎の指南書(精通)</t>
   </si>
   <si>
     <t>Rank.Rの炎属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Fire Guidebook (Expertise)</t>
+  </si>
+  <si>
+    <t>Obtain Rank R Fire Gear</t>
+  </si>
+  <si>
     <t>雷の指南書(精通)</t>
   </si>
   <si>
     <t>Rank.Rの雷属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Thunder Guidebook (Expertise)</t>
+  </si>
+  <si>
+    <t>Obtain Rank R Thunder Gear</t>
+  </si>
+  <si>
     <t>氷の指南書(精通)</t>
   </si>
   <si>
     <t>Rank.Rの氷属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Ice Guidebook (Expertise)</t>
+  </si>
+  <si>
+    <t>Obtain Rank R Ice Gear</t>
+  </si>
+  <si>
     <t>光の指南書(精通)</t>
   </si>
   <si>
     <t>Rank.Rの光属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Light Guidebook (Expertise)</t>
+  </si>
+  <si>
+    <t>Obtain Rank R Light Gear</t>
+  </si>
+  <si>
     <t>闇の指南書(精通)</t>
   </si>
   <si>
     <t>Rank.Rの闇属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Dark Guidebook (Expertise)</t>
+  </si>
+  <si>
+    <t>Obtain Rank R Dark Gear</t>
+  </si>
+  <si>
     <t>虹の指南書(熟練者)</t>
   </si>
   <si>
     <t>Rank.SRの装具を選んで入手</t>
   </si>
   <si>
+    <t>Rainbow Guidebook (Proficient)</t>
+  </si>
+  <si>
+    <t>Obtain Rank SR Gear</t>
+  </si>
+  <si>
     <t>炎の指南書(熟練者)</t>
   </si>
   <si>
     <t>Rank.SRの炎属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Fire Guidebook (Proficient)</t>
+  </si>
+  <si>
+    <t>Obtain Rank SR Fire Gear</t>
+  </si>
+  <si>
     <t>雷の指南書(熟練者)</t>
   </si>
   <si>
     <t>Rank.SRの雷属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Thunder Guidebook (Proficient)</t>
+  </si>
+  <si>
+    <t>Obtain Rank SR Thunder Gear</t>
+  </si>
+  <si>
     <t>氷の指南書(熟練者)</t>
   </si>
   <si>
     <t>Rank.SRの氷属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Ice Guidebook (Proficient)</t>
+  </si>
+  <si>
+    <t>Obtain Rank SR Ice Gear</t>
+  </si>
+  <si>
     <t>光の指南書(熟練者)</t>
   </si>
   <si>
     <t>Rank.SRの光属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Light Guidebook (Proficient)</t>
+  </si>
+  <si>
+    <t>Obtain Rank SR Light Gear</t>
+  </si>
+  <si>
     <t>闇の指南書(熟練者)</t>
   </si>
   <si>
     <t>Rank.SRの闇属性装具を選んで入手</t>
   </si>
   <si>
+    <t>Dark Guidebook (Proficient)</t>
+  </si>
+  <si>
+    <t>Obtain Rank SR Dark Gear</t>
+  </si>
+  <si>
     <t>虹の精霊輝石</t>
   </si>
   <si>
     <t>Rank.Nの強化魔法をランダムで入手</t>
   </si>
   <si>
+    <t>Rainbow Spirit Gem</t>
+  </si>
+  <si>
     <t>炎の精霊輝石</t>
   </si>
   <si>
     <t>Rank.Nの炎属性強化魔法をランダムで入手</t>
   </si>
   <si>
+    <t>Fire Spirit Gem</t>
+  </si>
+  <si>
     <t>雷の精霊輝石</t>
   </si>
   <si>
     <t>Rank.Nの雷属性強化魔法をランダムで入手</t>
   </si>
   <si>
+    <t>Thunder Spirit Gem</t>
+  </si>
+  <si>
     <t>氷の精霊輝石</t>
   </si>
   <si>
     <t>Rank.Nの氷属性強化魔法をランダムで入手</t>
   </si>
   <si>
+    <t>Ice Spirit Gem</t>
+  </si>
+  <si>
     <t>光の精霊輝石</t>
   </si>
   <si>
     <t>Rank.Nの光属性強化魔法をランダムで入手</t>
   </si>
   <si>
+    <t>Light Spirit Gem</t>
+  </si>
+  <si>
     <t>闇の精霊輝石</t>
   </si>
   <si>
     <t>Rank.Nの闇属性強化魔法をランダムで入手</t>
   </si>
   <si>
+    <t>Dark Spirit Gem</t>
+  </si>
+  <si>
     <t>妖精の祈り</t>
   </si>
   <si>
     <t>評価値+10</t>
   </si>
   <si>
+    <t>Fairy's Prayer</t>
+  </si>
+  <si>
+    <t>Evaluation +10</t>
+  </si>
+  <si>
     <t>月のかけら</t>
   </si>
   <si>
+    <t>Shard of the Moon</t>
+  </si>
+  <si>
     <t>商売の才覚書</t>
   </si>
   <si>
+    <t>Book of Business Talent</t>
+  </si>
+  <si>
     <t>メビウスの砂時計</t>
   </si>
   <si>
+    <t>Möbius Sandglass</t>
+  </si>
+  <si>
     <t>先陣の心得</t>
   </si>
   <si>
+    <t>Foremost Knowledge</t>
+  </si>
+  <si>
     <t>ヒスイの勾玉</t>
   </si>
   <si>
+    <t>Jade Talisman</t>
+  </si>
+  <si>
     <t>英傑の盾</t>
   </si>
   <si>
+    <t>Champion's Shield</t>
+  </si>
+  <si>
     <t>鷹の目</t>
   </si>
   <si>
+    <t>Eagle Eye</t>
+  </si>
+  <si>
     <t>ヒールユニット</t>
   </si>
   <si>
+    <t>Heal Unit</t>
+  </si>
+  <si>
     <t>金塊</t>
   </si>
   <si>
     <t>50(Nu)に換金できる</t>
   </si>
   <si>
+    <t>Gold Block</t>
+  </si>
+  <si>
+    <t>Can be exchanged for 50 Nu</t>
+  </si>
+  <si>
     <t>ダイアモンド</t>
   </si>
   <si>
     <t>200(Nu)に換金できる</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>Can be exchanged for 200 Nu</t>
   </si>
   <si>
     <t>初級指南書</t>
@@ -244,6 +412,13 @@
 Lvが10以下の場合は取得経験値が2倍になる</t>
   </si>
   <si>
+    <t>Beginner Guidebook</t>
+  </si>
+  <si>
+    <t>Gain 50 Exp
+If Lv is 10 or below, received EXP is doubled</t>
+  </si>
+  <si>
     <t>中級指南書</t>
   </si>
   <si>
@@ -251,6 +426,13 @@
 Lvが20以下の場合は取得経験値が2倍になる</t>
   </si>
   <si>
+    <t>Intermediate Guidebook</t>
+  </si>
+  <si>
+    <t>Gain 50 Exp
+If Lv is 20 or below, received EXP is doubled</t>
+  </si>
+  <si>
     <t>上級指南書</t>
   </si>
   <si>
@@ -258,6 +440,13 @@
 Lvが30以下の場合は取得経験値が2倍になる</t>
   </si>
   <si>
+    <t>Advanced Guidebook</t>
+  </si>
+  <si>
+    <t>Gain 50 Exp
+If Lv is 30 or below, received EXP is doubled</t>
+  </si>
+  <si>
     <t>特級指南書</t>
   </si>
   <si>
@@ -265,70 +454,143 @@
 Lvが40以下の場合は取得経験値が2倍になる</t>
   </si>
   <si>
+    <t>Expert Guidebook</t>
+  </si>
+  <si>
+    <t>Gain 50 Exp
+If Lv is 40 or below, received EXP is doubled</t>
+  </si>
+  <si>
     <t>レッドスピネル</t>
   </si>
   <si>
     <t>炎属性の適正アップ</t>
   </si>
   <si>
+    <t>Red Spinel</t>
+  </si>
+  <si>
+    <t>Increase Fire Affinity</t>
+  </si>
+  <si>
     <t>シトリン</t>
   </si>
   <si>
     <t>雷属性の適正アップ</t>
   </si>
   <si>
+    <t>Citrine</t>
+  </si>
+  <si>
+    <t>Increase Thunder Affinity</t>
+  </si>
+  <si>
     <t>タンザナイト</t>
   </si>
   <si>
     <t>氷属性の適正アップ</t>
   </si>
   <si>
+    <t>Tsavorite</t>
+  </si>
+  <si>
+    <t>Increase Ice Affinity</t>
+  </si>
+  <si>
     <t>ムーンストーン</t>
   </si>
   <si>
     <t>光属性の適正アップ</t>
   </si>
   <si>
+    <t>Moonstone</t>
+  </si>
+  <si>
+    <t>Increase Light Affinity</t>
+  </si>
+  <si>
     <t>ブラッドストーン</t>
   </si>
   <si>
     <t>闇属性の適正アップ</t>
   </si>
   <si>
+    <t>Bloodstone</t>
+  </si>
+  <si>
+    <t>Increase Dark Affinity</t>
+  </si>
+  <si>
     <t>生命の雫</t>
   </si>
   <si>
     <t>最大Hpを1アップ</t>
   </si>
   <si>
+    <t>Drop of Life</t>
+  </si>
+  <si>
+    <t>Max HP +1</t>
+  </si>
+  <si>
     <t>活力の果実</t>
   </si>
   <si>
     <t>最大Cpを１アップ</t>
   </si>
   <si>
+    <t>Vitality Fruit</t>
+  </si>
+  <si>
+    <t>Max CP +1</t>
+  </si>
+  <si>
     <t>力のたすき</t>
   </si>
   <si>
     <t>Atkを１アップ</t>
   </si>
   <si>
+    <t>Band of Power</t>
+  </si>
+  <si>
+    <t>ATK +1</t>
+  </si>
+  <si>
     <t>守りのお守り</t>
   </si>
   <si>
     <t>Defを１アップ</t>
   </si>
   <si>
+    <t>Good Luck Charm</t>
+  </si>
+  <si>
+    <t>DEF +1</t>
+  </si>
+  <si>
     <t>妖精の羽</t>
   </si>
   <si>
     <t>Spdを１アップ</t>
   </si>
   <si>
+    <t>Fairy's Wing</t>
+  </si>
+  <si>
+    <t>SPD +1</t>
+  </si>
+  <si>
     <t>マスタープルフ</t>
   </si>
   <si>
     <t>クラスチェンジできる</t>
+  </si>
+  <si>
+    <t>Master Puff</t>
+  </si>
+  <si>
+    <t>Can Change Class</t>
   </si>
   <si>
     <t>ダークボトル</t>
@@ -338,6 +600,13 @@
 一定期間の間エンカウントしやすくなる</t>
   </si>
   <si>
+    <t>Dark Bottle</t>
+  </si>
+  <si>
+    <t>&lt;Dungeon Exclusive Item&gt;
+Increases encounter rate for a certain period of time</t>
+  </si>
+  <si>
     <t>ホーリーボトル</t>
   </si>
   <si>
@@ -345,6 +614,13 @@
 一定期間の間エンカウントしにくくなる</t>
   </si>
   <si>
+    <t>Holy Bottle</t>
+  </si>
+  <si>
+    <t>&lt;Dungeon Exclusive Item&gt;
+Decreases encounter rate for a certain period of time</t>
+  </si>
+  <si>
     <t>聖者の祈祷酒</t>
   </si>
   <si>
@@ -352,10 +628,23 @@
 一定期間の間エンカウントしなくなる</t>
   </si>
   <si>
+    <t>Saint's Prayer Wine</t>
+  </si>
+  <si>
+    <t>&lt;Dungeon Exclusive Item&gt;
+Prevents encounters for a certain period of time</t>
+  </si>
+  <si>
     <t>隠遁のヴェール</t>
   </si>
   <si>
     <t>ダンジョンにいられる猶予ターンを10増やす</t>
+  </si>
+  <si>
+    <t>Hermit's Veil</t>
+  </si>
+  <si>
+    <t>Increase the number of turns you can stay in the dungeon by 10</t>
   </si>
   <si>
     <t>ポーション</t>
@@ -365,11 +654,25 @@
 仲間全員のHpを20回復する</t>
   </si>
   <si>
+    <t>Potion</t>
+  </si>
+  <si>
+    <t>&lt;Dungeon Exclusive Item&gt;
+Heals all allies' HP by 20</t>
+  </si>
+  <si>
     <t>ハイポーション</t>
   </si>
   <si>
     <t>&lt;ダンジョン専用アイテム&gt;
 仲間全員のHpを50回復する</t>
+  </si>
+  <si>
+    <t>High Potion</t>
+  </si>
+  <si>
+    <t>&lt;Dungeon Exclusive Item&gt;
+Heals all allies' HP by 50</t>
   </si>
   <si>
     <t>Type</t>
@@ -407,9 +710,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -428,14 +731,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -443,15 +738,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -464,32 +768,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -511,8 +791,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -522,37 +848,6 @@
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -566,9 +861,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -587,13 +890,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,79 +926,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,7 +950,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,13 +962,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -725,49 +1070,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,26 +1081,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -816,17 +1099,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -849,8 +1126,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -878,6 +1155,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -886,145 +1189,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2688,7 +2991,7 @@
   <cols>
     <col min="2" max="2" width="19.8181818181818" customWidth="1"/>
     <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
-    <col min="6" max="6" width="17.1909090909091" customWidth="1"/>
+    <col min="6" max="6" width="30.3272727272727" customWidth="1"/>
     <col min="7" max="7" width="40.1636363636364" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2720,10 +3023,10 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2731,16 +3034,16 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2748,16 +3051,16 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2765,16 +3068,16 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2782,16 +3085,16 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2799,16 +3102,16 @@
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2816,16 +3119,16 @@
         <v>1100</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2833,16 +3136,16 @@
         <v>1110</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2850,16 +3153,16 @@
         <v>1120</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2867,16 +3170,16 @@
         <v>1130</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2884,16 +3187,16 @@
         <v>1140</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2901,16 +3204,16 @@
         <v>1150</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2918,16 +3221,16 @@
         <v>1200</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2935,16 +3238,16 @@
         <v>1210</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2952,16 +3255,16 @@
         <v>1220</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2969,16 +3272,16 @@
         <v>1230</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2986,16 +3289,16 @@
         <v>1240</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3003,16 +3306,16 @@
         <v>1250</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3020,16 +3323,16 @@
         <v>1300</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3037,16 +3340,16 @@
         <v>1310</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3054,16 +3357,16 @@
         <v>1320</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3071,16 +3374,16 @@
         <v>1330</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3088,16 +3391,16 @@
         <v>1340</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G24" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3105,16 +3408,16 @@
         <v>1350</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="G25" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3122,16 +3425,16 @@
         <v>2010</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3139,16 +3442,16 @@
         <v>2020</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="G27" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3156,16 +3459,16 @@
         <v>2030</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="G28" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3173,16 +3476,16 @@
         <v>2040</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="G29" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3190,16 +3493,16 @@
         <v>2050</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="G30" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3207,16 +3510,16 @@
         <v>2060</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F31" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3224,16 +3527,16 @@
         <v>2070</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="G32" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3241,16 +3544,16 @@
         <v>2080</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="G33" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3258,16 +3561,16 @@
         <v>2130</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F34" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="G34" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3275,16 +3578,16 @@
         <v>3010</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3292,16 +3595,16 @@
         <v>3020</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" ht="39" spans="1:7">
@@ -3309,16 +3612,16 @@
         <v>4010</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="F37" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" ht="39" spans="1:7">
@@ -3326,16 +3629,16 @@
         <v>4020</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="F38" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" ht="39" spans="1:7">
@@ -3343,16 +3646,16 @@
         <v>4030</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="F39" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" ht="39" spans="1:7">
@@ -3360,16 +3663,16 @@
         <v>4040</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3377,16 +3680,16 @@
         <v>4110</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="F41" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="G41" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3394,16 +3697,16 @@
         <v>4120</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="F42" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="G42" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3411,16 +3714,16 @@
         <v>4130</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="F43" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="G43" t="s">
-        <v>86</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3428,16 +3731,16 @@
         <v>4140</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="F44" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="G44" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3445,16 +3748,16 @@
         <v>4150</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="F45" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="G45" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3462,16 +3765,16 @@
         <v>4210</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="F46" t="s">
-        <v>91</v>
+        <v>167</v>
       </c>
       <c r="G46" t="s">
-        <v>92</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3479,16 +3782,16 @@
         <v>4220</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="F47" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="G47" t="s">
-        <v>94</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3496,16 +3799,16 @@
         <v>4230</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>173</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="F48" t="s">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="G48" t="s">
-        <v>96</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3513,16 +3816,16 @@
         <v>4240</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
       <c r="F49" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="G49" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3530,16 +3833,16 @@
         <v>4250</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>181</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="F50" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="G50" t="s">
-        <v>100</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3547,16 +3850,16 @@
         <v>4310</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="F51" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="G51" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" ht="39" spans="1:7">
@@ -3564,16 +3867,16 @@
         <v>5010</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="F52" t="s">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>104</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" ht="39" spans="1:7">
@@ -3581,16 +3884,16 @@
         <v>5020</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="F53" t="s">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>106</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" ht="39" spans="1:7">
@@ -3598,16 +3901,16 @@
         <v>5030</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="F54" t="s">
-        <v>107</v>
+        <v>199</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>108</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3615,16 +3918,16 @@
         <v>5040</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="C55" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="F55" t="s">
-        <v>109</v>
+        <v>203</v>
       </c>
       <c r="G55" t="s">
-        <v>110</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" ht="26" spans="1:7">
@@ -3632,16 +3935,16 @@
         <v>5050</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>205</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="F56" t="s">
-        <v>111</v>
+        <v>207</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>112</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" ht="26" spans="1:7">
@@ -3649,16 +3952,16 @@
         <v>5060</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>114</v>
+        <v>210</v>
       </c>
       <c r="F57" t="s">
-        <v>113</v>
+        <v>211</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>114</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3678,7 +3981,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3686,10 +3989,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3697,10 +4000,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>216</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3708,10 +4011,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>218</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>121</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3719,7 +4022,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3727,7 +4030,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3735,7 +4038,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -710,10 +710,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -731,47 +731,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -791,25 +755,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -823,9 +785,47 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -838,7 +838,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -853,23 +869,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -896,7 +896,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -908,25 +998,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -938,139 +1064,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1108,6 +1108,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1132,6 +1147,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1146,41 +1181,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1189,145 +1189,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="225">
   <si>
     <t>Id</t>
   </si>
@@ -373,6 +373,12 @@
   </si>
   <si>
     <t>Eagle Eye</t>
+  </si>
+  <si>
+    <t>ラーニングピアス</t>
+  </si>
+  <si>
+    <t>Learning Pierce</t>
   </si>
   <si>
     <t>ヒールユニット</t>
@@ -710,10 +716,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -728,22 +734,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -762,6 +752,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -770,15 +783,46 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -800,6 +844,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -807,38 +858,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -853,25 +874,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -890,13 +896,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -908,13 +926,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -932,7 +950,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -950,43 +1046,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1004,73 +1076,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1081,6 +1087,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1095,30 +1125,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1156,17 +1162,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1181,6 +1176,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1189,7 +1195,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1198,136 +1204,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1663,7 +1669,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2427,7 +2433,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>2130</v>
+        <v>2090</v>
       </c>
       <c r="B34">
         <v>58</v>
@@ -2436,7 +2442,7 @@
         <v>20</v>
       </c>
       <c r="D34">
-        <v>310130</v>
+        <v>310090</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2450,16 +2456,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>3010</v>
+        <v>2130</v>
       </c>
       <c r="B35">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="C35">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D35">
-        <v>50</v>
+        <v>310130</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2473,7 +2479,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B36">
         <v>231</v>
@@ -2482,7 +2488,7 @@
         <v>30</v>
       </c>
       <c r="D36">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2496,30 +2502,30 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B37">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C37">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="E37">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>10</v>
-      </c>
-      <c r="G37" s="1">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B38">
         <v>220</v>
@@ -2534,15 +2540,15 @@
         <v>50</v>
       </c>
       <c r="F38">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G38" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="B39">
         <v>220</v>
@@ -2557,15 +2563,15 @@
         <v>50</v>
       </c>
       <c r="F39">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G39" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="B40">
         <v>220</v>
@@ -2580,30 +2586,30 @@
         <v>50</v>
       </c>
       <c r="F40">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G40" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>4110</v>
+        <v>4040</v>
       </c>
       <c r="B41">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G41" s="1">
         <v>200</v>
@@ -2611,7 +2617,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B42">
         <v>224</v>
@@ -2623,7 +2629,7 @@
         <v>20</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -2634,7 +2640,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B43">
         <v>224</v>
@@ -2646,7 +2652,7 @@
         <v>20</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -2657,7 +2663,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B44">
         <v>224</v>
@@ -2669,7 +2675,7 @@
         <v>20</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -2680,7 +2686,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B45">
         <v>224</v>
@@ -2692,7 +2698,7 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -2703,19 +2709,19 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>4210</v>
+        <v>4150</v>
       </c>
       <c r="B46">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C46">
         <v>40</v>
       </c>
       <c r="D46">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -2726,10 +2732,10 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="B47">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C47">
         <v>40</v>
@@ -2738,7 +2744,7 @@
         <v>30</v>
       </c>
       <c r="E47">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -2749,10 +2755,10 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>4230</v>
+        <v>4220</v>
       </c>
       <c r="B48">
-        <v>117</v>
+        <v>202</v>
       </c>
       <c r="C48">
         <v>40</v>
@@ -2761,7 +2767,7 @@
         <v>30</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -2772,10 +2778,10 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>4240</v>
+        <v>4230</v>
       </c>
       <c r="B49">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C49">
         <v>40</v>
@@ -2784,7 +2790,7 @@
         <v>30</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -2795,10 +2801,10 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>4250</v>
+        <v>4240</v>
       </c>
       <c r="B50">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="C50">
         <v>40</v>
@@ -2807,7 +2813,7 @@
         <v>30</v>
       </c>
       <c r="E50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -2818,53 +2824,53 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>4310</v>
+        <v>4250</v>
       </c>
       <c r="B51">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="C51">
         <v>40</v>
       </c>
       <c r="D51">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="B52">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="C52">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D52">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E52">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B53">
         <v>125</v>
@@ -2876,7 +2882,7 @@
         <v>50</v>
       </c>
       <c r="E53">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F53">
         <v>25</v>
@@ -2887,7 +2893,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B54">
         <v>125</v>
@@ -2899,7 +2905,7 @@
         <v>50</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F54">
         <v>25</v>
@@ -2910,7 +2916,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="B55">
         <v>125</v>
@@ -2919,13 +2925,13 @@
         <v>50</v>
       </c>
       <c r="D55">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E55">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G55" s="1">
         <v>20</v>
@@ -2933,7 +2939,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="B56">
         <v>125</v>
@@ -2942,21 +2948,21 @@
         <v>50</v>
       </c>
       <c r="D56">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E56">
+        <v>10</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
         <v>20</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="B57">
         <v>125</v>
@@ -2968,12 +2974,35 @@
         <v>70</v>
       </c>
       <c r="E57">
+        <v>20</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
         <v>50</v>
       </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>5060</v>
+      </c>
+      <c r="B58">
+        <v>125</v>
+      </c>
+      <c r="C58">
+        <v>50</v>
+      </c>
+      <c r="D58">
+        <v>70</v>
+      </c>
+      <c r="E58">
+        <v>50</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2986,7 +3015,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="19.8181818181818" customWidth="1"/>
@@ -3558,7 +3587,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>2130</v>
+        <v>2090</v>
       </c>
       <c r="B34" t="s">
         <v>119</v>
@@ -3575,393 +3604,410 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>3010</v>
-      </c>
-      <c r="B35" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B35" t="s">
         <v>121</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35" t="s">
         <v>122</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>124</v>
+      <c r="G35" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
+        <v>3010</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
         <v>3020</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F36" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="37" ht="39" spans="1:7">
-      <c r="A37">
-        <v>4010</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="F37" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="G37" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="F37" t="s">
-        <v>131</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="38" ht="39" spans="1:7">
       <c r="A38">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="G38" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="F38" t="s">
-        <v>135</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="39" ht="39" spans="1:7">
       <c r="A39">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="B39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F39" t="s">
         <v>137</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="G39" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F39" t="s">
-        <v>139</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="40" ht="39" spans="1:7">
       <c r="A40">
+        <v>4030</v>
+      </c>
+      <c r="B40" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F40" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" ht="39" spans="1:7">
+      <c r="A41">
         <v>4040</v>
       </c>
-      <c r="B40" t="s">
-        <v>141</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="B41" t="s">
         <v>143</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>4110</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="F41" t="s">
         <v>145</v>
       </c>
-      <c r="C41" t="s">
+      <c r="G41" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="F41" t="s">
-        <v>147</v>
-      </c>
-      <c r="G41" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B42" t="s">
+        <v>147</v>
+      </c>
+      <c r="C42" t="s">
+        <v>148</v>
+      </c>
+      <c r="F42" t="s">
         <v>149</v>
       </c>
-      <c r="C42" t="s">
+      <c r="G42" t="s">
         <v>150</v>
-      </c>
-      <c r="F42" t="s">
-        <v>151</v>
-      </c>
-      <c r="G42" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B43" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" t="s">
+      <c r="G43" t="s">
         <v>154</v>
-      </c>
-      <c r="F43" t="s">
-        <v>155</v>
-      </c>
-      <c r="G43" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B44" t="s">
+        <v>155</v>
+      </c>
+      <c r="C44" t="s">
+        <v>156</v>
+      </c>
+      <c r="F44" t="s">
         <v>157</v>
       </c>
-      <c r="C44" t="s">
+      <c r="G44" t="s">
         <v>158</v>
-      </c>
-      <c r="F44" t="s">
-        <v>159</v>
-      </c>
-      <c r="G44" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F45" t="s">
         <v>161</v>
       </c>
-      <c r="C45" t="s">
+      <c r="G45" t="s">
         <v>162</v>
-      </c>
-      <c r="F45" t="s">
-        <v>163</v>
-      </c>
-      <c r="G45" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>4210</v>
+        <v>4150</v>
       </c>
       <c r="B46" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46" t="s">
+        <v>164</v>
+      </c>
+      <c r="F46" t="s">
         <v>165</v>
       </c>
-      <c r="C46" t="s">
+      <c r="G46" t="s">
         <v>166</v>
-      </c>
-      <c r="F46" t="s">
-        <v>167</v>
-      </c>
-      <c r="G46" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="B47" t="s">
+        <v>167</v>
+      </c>
+      <c r="C47" t="s">
+        <v>168</v>
+      </c>
+      <c r="F47" t="s">
         <v>169</v>
       </c>
-      <c r="C47" t="s">
+      <c r="G47" t="s">
         <v>170</v>
-      </c>
-      <c r="F47" t="s">
-        <v>171</v>
-      </c>
-      <c r="G47" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>4230</v>
+        <v>4220</v>
       </c>
       <c r="B48" t="s">
+        <v>171</v>
+      </c>
+      <c r="C48" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" t="s">
         <v>173</v>
       </c>
-      <c r="C48" t="s">
+      <c r="G48" t="s">
         <v>174</v>
-      </c>
-      <c r="F48" t="s">
-        <v>175</v>
-      </c>
-      <c r="G48" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>4240</v>
+        <v>4230</v>
       </c>
       <c r="B49" t="s">
+        <v>175</v>
+      </c>
+      <c r="C49" t="s">
+        <v>176</v>
+      </c>
+      <c r="F49" t="s">
         <v>177</v>
       </c>
-      <c r="C49" t="s">
+      <c r="G49" t="s">
         <v>178</v>
-      </c>
-      <c r="F49" t="s">
-        <v>179</v>
-      </c>
-      <c r="G49" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>4250</v>
+        <v>4240</v>
       </c>
       <c r="B50" t="s">
+        <v>179</v>
+      </c>
+      <c r="C50" t="s">
+        <v>180</v>
+      </c>
+      <c r="F50" t="s">
         <v>181</v>
       </c>
-      <c r="C50" t="s">
+      <c r="G50" t="s">
         <v>182</v>
-      </c>
-      <c r="F50" t="s">
-        <v>183</v>
-      </c>
-      <c r="G50" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
+        <v>4250</v>
+      </c>
+      <c r="B51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" t="s">
+        <v>184</v>
+      </c>
+      <c r="F51" t="s">
+        <v>185</v>
+      </c>
+      <c r="G51" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
         <v>4310</v>
       </c>
-      <c r="B51" t="s">
-        <v>185</v>
-      </c>
-      <c r="C51" t="s">
-        <v>186</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="B52" t="s">
         <v>187</v>
       </c>
-      <c r="G51" t="s">
+      <c r="C52" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="52" ht="39" spans="1:7">
-      <c r="A52">
-        <v>5010</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="F52" t="s">
         <v>189</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="G52" t="s">
         <v>190</v>
-      </c>
-      <c r="F52" t="s">
-        <v>191</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="53" ht="39" spans="1:7">
       <c r="A53">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B53" t="s">
+        <v>191</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F53" t="s">
         <v>193</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="G53" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="F53" t="s">
-        <v>195</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="54" ht="39" spans="1:7">
       <c r="A54">
+        <v>5020</v>
+      </c>
+      <c r="B54" t="s">
+        <v>195</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F54" t="s">
+        <v>197</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55" ht="39" spans="1:7">
+      <c r="A55">
         <v>5030</v>
       </c>
-      <c r="B54" t="s">
-        <v>197</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="B55" t="s">
         <v>199</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
+      <c r="F55" t="s">
+        <v>201</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
         <v>5040</v>
       </c>
-      <c r="B55" t="s">
-        <v>201</v>
-      </c>
-      <c r="C55" t="s">
-        <v>202</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="B56" t="s">
         <v>203</v>
       </c>
-      <c r="G55" t="s">
+      <c r="C56" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="56" ht="26" spans="1:7">
-      <c r="A56">
-        <v>5050</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="F56" t="s">
         <v>205</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="G56" t="s">
         <v>206</v>
-      </c>
-      <c r="F56" t="s">
-        <v>207</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="57" ht="26" spans="1:7">
       <c r="A57">
+        <v>5050</v>
+      </c>
+      <c r="B57" t="s">
+        <v>207</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F57" t="s">
+        <v>209</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" ht="26" spans="1:7">
+      <c r="A58">
         <v>5060</v>
       </c>
-      <c r="B57" t="s">
-        <v>209</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="B58" t="s">
         <v>211</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>212</v>
+      </c>
+      <c r="F58" t="s">
+        <v>213</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -3981,7 +4027,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3989,10 +4035,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4000,10 +4046,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4011,10 +4057,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -4022,7 +4068,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4030,7 +4076,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4038,7 +4084,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="227">
   <si>
     <t>Id</t>
   </si>
@@ -379,6 +379,12 @@
   </si>
   <si>
     <t>Learning Pierce</t>
+  </si>
+  <si>
+    <t>セブンズストーン</t>
+  </si>
+  <si>
+    <t>Seven`s Stone</t>
   </si>
   <si>
     <t>ヒールユニット</t>
@@ -737,9 +743,84 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -754,7 +835,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -768,15 +864,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -796,90 +886,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -896,7 +902,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -908,25 +926,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -944,7 +944,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -956,61 +1046,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1022,13 +1058,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1040,43 +1076,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1090,26 +1096,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1144,11 +1135,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1157,7 +1154,27 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1176,17 +1193,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1195,7 +1201,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1204,136 +1210,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1669,7 +1675,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2456,7 +2462,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>2130</v>
+        <v>2100</v>
       </c>
       <c r="B35">
         <v>58</v>
@@ -2465,7 +2471,7 @@
         <v>20</v>
       </c>
       <c r="D35">
-        <v>310130</v>
+        <v>310100</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2479,16 +2485,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>3010</v>
+        <v>2130</v>
       </c>
       <c r="B36">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="C36">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D36">
-        <v>50</v>
+        <v>310130</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2502,7 +2508,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B37">
         <v>231</v>
@@ -2511,7 +2517,7 @@
         <v>30</v>
       </c>
       <c r="D37">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2525,30 +2531,30 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B38">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C38">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="E38">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>10</v>
-      </c>
-      <c r="G38" s="1">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B39">
         <v>220</v>
@@ -2563,15 +2569,15 @@
         <v>50</v>
       </c>
       <c r="F39">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G39" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="B40">
         <v>220</v>
@@ -2586,15 +2592,15 @@
         <v>50</v>
       </c>
       <c r="F40">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G40" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="B41">
         <v>220</v>
@@ -2609,30 +2615,30 @@
         <v>50</v>
       </c>
       <c r="F41">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G41" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>4110</v>
+        <v>4040</v>
       </c>
       <c r="B42">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C42">
         <v>40</v>
       </c>
       <c r="D42">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G42" s="1">
         <v>200</v>
@@ -2640,7 +2646,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B43">
         <v>224</v>
@@ -2652,7 +2658,7 @@
         <v>20</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -2663,7 +2669,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B44">
         <v>224</v>
@@ -2675,7 +2681,7 @@
         <v>20</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -2686,7 +2692,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B45">
         <v>224</v>
@@ -2698,7 +2704,7 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -2709,7 +2715,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B46">
         <v>224</v>
@@ -2721,7 +2727,7 @@
         <v>20</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -2732,19 +2738,19 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>4210</v>
+        <v>4150</v>
       </c>
       <c r="B47">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C47">
         <v>40</v>
       </c>
       <c r="D47">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -2755,10 +2761,10 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="B48">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C48">
         <v>40</v>
@@ -2767,7 +2773,7 @@
         <v>30</v>
       </c>
       <c r="E48">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -2778,10 +2784,10 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>4230</v>
+        <v>4220</v>
       </c>
       <c r="B49">
-        <v>117</v>
+        <v>202</v>
       </c>
       <c r="C49">
         <v>40</v>
@@ -2790,7 +2796,7 @@
         <v>30</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -2801,10 +2807,10 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>4240</v>
+        <v>4230</v>
       </c>
       <c r="B50">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C50">
         <v>40</v>
@@ -2813,7 +2819,7 @@
         <v>30</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -2824,10 +2830,10 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>4250</v>
+        <v>4240</v>
       </c>
       <c r="B51">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="C51">
         <v>40</v>
@@ -2836,7 +2842,7 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -2847,53 +2853,53 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>4310</v>
+        <v>4250</v>
       </c>
       <c r="B52">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="C52">
         <v>40</v>
       </c>
       <c r="D52">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="B53">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="C53">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D53">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E53">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B54">
         <v>125</v>
@@ -2905,7 +2911,7 @@
         <v>50</v>
       </c>
       <c r="E54">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F54">
         <v>25</v>
@@ -2916,7 +2922,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B55">
         <v>125</v>
@@ -2928,7 +2934,7 @@
         <v>50</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F55">
         <v>25</v>
@@ -2939,7 +2945,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="B56">
         <v>125</v>
@@ -2948,13 +2954,13 @@
         <v>50</v>
       </c>
       <c r="D56">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E56">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G56" s="1">
         <v>20</v>
@@ -2962,7 +2968,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="B57">
         <v>125</v>
@@ -2971,21 +2977,21 @@
         <v>50</v>
       </c>
       <c r="D57">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E57">
+        <v>10</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
         <v>20</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="B58">
         <v>125</v>
@@ -2997,12 +3003,35 @@
         <v>70</v>
       </c>
       <c r="E58">
+        <v>20</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
         <v>50</v>
       </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>5060</v>
+      </c>
+      <c r="B59">
+        <v>125</v>
+      </c>
+      <c r="C59">
+        <v>50</v>
+      </c>
+      <c r="D59">
+        <v>70</v>
+      </c>
+      <c r="E59">
+        <v>50</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
         <v>100</v>
       </c>
     </row>
@@ -3015,7 +3044,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="19.8181818181818" customWidth="1"/>
@@ -3604,7 +3633,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>2130</v>
+        <v>2100</v>
       </c>
       <c r="B35" t="s">
         <v>121</v>
@@ -3621,393 +3650,410 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>3010</v>
-      </c>
-      <c r="B36" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B36" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" t="s">
         <v>124</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>126</v>
+      <c r="G36" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
+        <v>3010</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
         <v>3020</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="38" ht="39" spans="1:7">
-      <c r="A38">
-        <v>4010</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="F38" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="G38" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="F38" t="s">
-        <v>133</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="39" ht="39" spans="1:7">
       <c r="A39">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B39" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F39" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="G39" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="F39" t="s">
-        <v>137</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="40" ht="39" spans="1:7">
       <c r="A40">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="B40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F40" t="s">
         <v>139</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="G40" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="F40" t="s">
-        <v>141</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="41" ht="39" spans="1:7">
       <c r="A41">
+        <v>4030</v>
+      </c>
+      <c r="B41" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F41" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" ht="39" spans="1:7">
+      <c r="A42">
         <v>4040</v>
       </c>
-      <c r="B41" t="s">
-        <v>143</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="B42" t="s">
         <v>145</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>4110</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="F42" t="s">
         <v>147</v>
       </c>
-      <c r="C42" t="s">
+      <c r="G42" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="F42" t="s">
-        <v>149</v>
-      </c>
-      <c r="G42" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B43" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" t="s">
         <v>151</v>
       </c>
-      <c r="C43" t="s">
+      <c r="G43" t="s">
         <v>152</v>
-      </c>
-      <c r="F43" t="s">
-        <v>153</v>
-      </c>
-      <c r="G43" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B44" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" t="s">
+        <v>154</v>
+      </c>
+      <c r="F44" t="s">
         <v>155</v>
       </c>
-      <c r="C44" t="s">
+      <c r="G44" t="s">
         <v>156</v>
-      </c>
-      <c r="F44" t="s">
-        <v>157</v>
-      </c>
-      <c r="G44" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B45" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" t="s">
+        <v>158</v>
+      </c>
+      <c r="F45" t="s">
         <v>159</v>
       </c>
-      <c r="C45" t="s">
+      <c r="G45" t="s">
         <v>160</v>
-      </c>
-      <c r="F45" t="s">
-        <v>161</v>
-      </c>
-      <c r="G45" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" t="s">
+        <v>162</v>
+      </c>
+      <c r="F46" t="s">
         <v>163</v>
       </c>
-      <c r="C46" t="s">
+      <c r="G46" t="s">
         <v>164</v>
-      </c>
-      <c r="F46" t="s">
-        <v>165</v>
-      </c>
-      <c r="G46" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>4210</v>
+        <v>4150</v>
       </c>
       <c r="B47" t="s">
+        <v>165</v>
+      </c>
+      <c r="C47" t="s">
+        <v>166</v>
+      </c>
+      <c r="F47" t="s">
         <v>167</v>
       </c>
-      <c r="C47" t="s">
+      <c r="G47" t="s">
         <v>168</v>
-      </c>
-      <c r="F47" t="s">
-        <v>169</v>
-      </c>
-      <c r="G47" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="B48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C48" t="s">
+        <v>170</v>
+      </c>
+      <c r="F48" t="s">
         <v>171</v>
       </c>
-      <c r="C48" t="s">
+      <c r="G48" t="s">
         <v>172</v>
-      </c>
-      <c r="F48" t="s">
-        <v>173</v>
-      </c>
-      <c r="G48" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>4230</v>
+        <v>4220</v>
       </c>
       <c r="B49" t="s">
+        <v>173</v>
+      </c>
+      <c r="C49" t="s">
+        <v>174</v>
+      </c>
+      <c r="F49" t="s">
         <v>175</v>
       </c>
-      <c r="C49" t="s">
+      <c r="G49" t="s">
         <v>176</v>
-      </c>
-      <c r="F49" t="s">
-        <v>177</v>
-      </c>
-      <c r="G49" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>4240</v>
+        <v>4230</v>
       </c>
       <c r="B50" t="s">
+        <v>177</v>
+      </c>
+      <c r="C50" t="s">
+        <v>178</v>
+      </c>
+      <c r="F50" t="s">
         <v>179</v>
       </c>
-      <c r="C50" t="s">
+      <c r="G50" t="s">
         <v>180</v>
-      </c>
-      <c r="F50" t="s">
-        <v>181</v>
-      </c>
-      <c r="G50" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>4250</v>
+        <v>4240</v>
       </c>
       <c r="B51" t="s">
+        <v>181</v>
+      </c>
+      <c r="C51" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" t="s">
         <v>183</v>
       </c>
-      <c r="C51" t="s">
+      <c r="G51" t="s">
         <v>184</v>
-      </c>
-      <c r="F51" t="s">
-        <v>185</v>
-      </c>
-      <c r="G51" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
+        <v>4250</v>
+      </c>
+      <c r="B52" t="s">
+        <v>185</v>
+      </c>
+      <c r="C52" t="s">
+        <v>186</v>
+      </c>
+      <c r="F52" t="s">
+        <v>187</v>
+      </c>
+      <c r="G52" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
         <v>4310</v>
       </c>
-      <c r="B52" t="s">
-        <v>187</v>
-      </c>
-      <c r="C52" t="s">
-        <v>188</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="B53" t="s">
         <v>189</v>
       </c>
-      <c r="G52" t="s">
+      <c r="C53" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="53" ht="39" spans="1:7">
-      <c r="A53">
-        <v>5010</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="F53" t="s">
         <v>191</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="G53" t="s">
         <v>192</v>
-      </c>
-      <c r="F53" t="s">
-        <v>193</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="54" ht="39" spans="1:7">
       <c r="A54">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B54" t="s">
+        <v>193</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F54" t="s">
         <v>195</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="G54" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="F54" t="s">
-        <v>197</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="55" ht="39" spans="1:7">
       <c r="A55">
+        <v>5020</v>
+      </c>
+      <c r="B55" t="s">
+        <v>197</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F55" t="s">
+        <v>199</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" ht="39" spans="1:7">
+      <c r="A56">
         <v>5030</v>
       </c>
-      <c r="B55" t="s">
-        <v>199</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="B56" t="s">
         <v>201</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
+      <c r="F56" t="s">
+        <v>203</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
         <v>5040</v>
       </c>
-      <c r="B56" t="s">
-        <v>203</v>
-      </c>
-      <c r="C56" t="s">
-        <v>204</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="B57" t="s">
         <v>205</v>
       </c>
-      <c r="G56" t="s">
+      <c r="C57" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="57" ht="26" spans="1:7">
-      <c r="A57">
-        <v>5050</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="F57" t="s">
         <v>207</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="G57" t="s">
         <v>208</v>
-      </c>
-      <c r="F57" t="s">
-        <v>209</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="58" ht="26" spans="1:7">
       <c r="A58">
+        <v>5050</v>
+      </c>
+      <c r="B58" t="s">
+        <v>209</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F58" t="s">
+        <v>211</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="59" ht="26" spans="1:7">
+      <c r="A59">
         <v>5060</v>
       </c>
-      <c r="B58" t="s">
-        <v>211</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="B59" t="s">
         <v>213</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>214</v>
+      </c>
+      <c r="F59" t="s">
+        <v>215</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -4027,7 +4073,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4035,10 +4081,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4046,10 +4092,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4057,10 +4103,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -4068,7 +4114,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4076,7 +4122,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4084,7 +4130,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -743,11 +743,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -760,14 +781,68 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -782,7 +857,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -796,14 +871,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -812,76 +879,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -902,7 +902,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -914,7 +944,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -926,19 +992,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -950,25 +1010,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -980,13 +1052,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -998,85 +1076,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1096,15 +1096,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1121,6 +1112,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -1131,6 +1137,35 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1154,42 +1189,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1201,7 +1201,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1210,136 +1210,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1744,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1813,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:7">
